--- a/Plano de trabalho/acompanhamento-app-do-amor.xlsx
+++ b/Plano de trabalho/acompanhamento-app-do-amor.xlsx
@@ -109,7 +109,7 @@
       </c>
       <c r="B2" s="0" t="inlineStr">
         <is>
-          <t>02/09/2026 23:20</t>
+          <t>05/09/2026 21:12</t>
         </is>
       </c>
       <c r="C2" s="0" t="inlineStr">
@@ -142,7 +142,7 @@
         </is>
       </c>
       <c r="B4" s="2">
-        <f>COUNTA('Plano Mestre'!A2:A108)</f>
+        <f>COUNTA('Plano Mestre'!A2:A123)</f>
         <v>0</v>
       </c>
       <c r="C4" s="0" t="inlineStr">
@@ -158,7 +158,7 @@
         </is>
       </c>
       <c r="B5" s="2">
-        <f>COUNTIF('Plano Mestre'!I2:I108,"Concluído")</f>
+        <f>COUNTIF('Plano Mestre'!I2:I123,"Concluído")</f>
         <v>0</v>
       </c>
       <c r="C5" s="0" t="inlineStr">
@@ -174,7 +174,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIF('Plano Mestre'!I2:I108,"Em andamento")</f>
+        <f>COUNTIF('Plano Mestre'!I2:I123,"Em andamento")</f>
         <v>0</v>
       </c>
       <c r="C6" s="0" t="inlineStr">
@@ -190,7 +190,7 @@
         </is>
       </c>
       <c r="B7" s="2">
-        <f>COUNTIF('Plano Mestre'!I2:I108,"Não iniciado")</f>
+        <f>COUNTIF('Plano Mestre'!I2:I123,"Não iniciado")</f>
         <v>0</v>
       </c>
       <c r="C7" s="0" t="inlineStr">
@@ -202,16 +202,16 @@
     <row r="8">
       <c r="A8" s="0" t="inlineStr">
         <is>
-          <t>Progresso geral</t>
+          <t>Progresso por status</t>
         </is>
       </c>
       <c r="B8" s="3">
-        <f>AVERAGE('Plano Mestre'!M2:M108)</f>
+        <f>AVERAGE('Plano Mestre'!M2:M123)</f>
         <v>0</v>
       </c>
       <c r="C8" s="0" t="inlineStr">
         <is>
-          <t>baseado no status</t>
+          <t>não mede prontidão do produto</t>
         </is>
       </c>
     </row>
@@ -222,7 +222,7 @@
         </is>
       </c>
       <c r="B9" s="2">
-        <f>SUM('Plano Mestre'!J2:J108)</f>
+        <f>SUM('Plano Mestre'!J2:J123)</f>
         <v>0</v>
       </c>
       <c r="C9" s="0" t="inlineStr">
@@ -272,11 +272,11 @@
         </is>
       </c>
       <c r="B12" s="2">
-        <f>COUNTIF('Plano Mestre'!B2:B108,"Descoberta")</f>
+        <f>COUNTIF('Plano Mestre'!B2:B123,"Descoberta")</f>
         <v>0</v>
       </c>
       <c r="C12" s="2">
-        <f>COUNTIFS('Plano Mestre'!B2:B108,"Descoberta",'Plano Mestre'!I2:I108,"Concluído")</f>
+        <f>COUNTIFS('Plano Mestre'!B2:B123,"Descoberta",'Plano Mestre'!I2:I123,"Concluído")</f>
         <v>0</v>
       </c>
     </row>
@@ -287,11 +287,11 @@
         </is>
       </c>
       <c r="B13" s="2">
-        <f>COUNTIF('Plano Mestre'!B2:B108,"Planejamento")</f>
+        <f>COUNTIF('Plano Mestre'!B2:B123,"Planejamento")</f>
         <v>0</v>
       </c>
       <c r="C13" s="2">
-        <f>COUNTIFS('Plano Mestre'!B2:B108,"Planejamento",'Plano Mestre'!I2:I108,"Concluído")</f>
+        <f>COUNTIFS('Plano Mestre'!B2:B123,"Planejamento",'Plano Mestre'!I2:I123,"Concluído")</f>
         <v>0</v>
       </c>
     </row>
@@ -302,11 +302,11 @@
         </is>
       </c>
       <c r="B14" s="2">
-        <f>COUNTIF('Plano Mestre'!B2:B108,"Marca")</f>
+        <f>COUNTIF('Plano Mestre'!B2:B123,"Marca")</f>
         <v>0</v>
       </c>
       <c r="C14" s="2">
-        <f>COUNTIFS('Plano Mestre'!B2:B108,"Marca",'Plano Mestre'!I2:I108,"Concluído")</f>
+        <f>COUNTIFS('Plano Mestre'!B2:B123,"Marca",'Plano Mestre'!I2:I123,"Concluído")</f>
         <v>0</v>
       </c>
     </row>
@@ -317,11 +317,11 @@
         </is>
       </c>
       <c r="B15" s="2">
-        <f>COUNTIF('Plano Mestre'!B2:B108,"UX/UI")</f>
+        <f>COUNTIF('Plano Mestre'!B2:B123,"UX/UI")</f>
         <v>0</v>
       </c>
       <c r="C15" s="2">
-        <f>COUNTIFS('Plano Mestre'!B2:B108,"UX/UI",'Plano Mestre'!I2:I108,"Concluído")</f>
+        <f>COUNTIFS('Plano Mestre'!B2:B123,"UX/UI",'Plano Mestre'!I2:I123,"Concluído")</f>
         <v>0</v>
       </c>
     </row>
@@ -332,11 +332,11 @@
         </is>
       </c>
       <c r="B16" s="2">
-        <f>COUNTIF('Plano Mestre'!B2:B108,"Arquitetura")</f>
+        <f>COUNTIF('Plano Mestre'!B2:B123,"Arquitetura")</f>
         <v>0</v>
       </c>
       <c r="C16" s="2">
-        <f>COUNTIFS('Plano Mestre'!B2:B108,"Arquitetura",'Plano Mestre'!I2:I108,"Concluído")</f>
+        <f>COUNTIFS('Plano Mestre'!B2:B123,"Arquitetura",'Plano Mestre'!I2:I123,"Concluído")</f>
         <v>0</v>
       </c>
     </row>
@@ -347,11 +347,11 @@
         </is>
       </c>
       <c r="B17" s="2">
-        <f>COUNTIF('Plano Mestre'!B2:B108,"Infraestrutura")</f>
+        <f>COUNTIF('Plano Mestre'!B2:B123,"Infraestrutura")</f>
         <v>0</v>
       </c>
       <c r="C17" s="2">
-        <f>COUNTIFS('Plano Mestre'!B2:B108,"Infraestrutura",'Plano Mestre'!I2:I108,"Concluído")</f>
+        <f>COUNTIFS('Plano Mestre'!B2:B123,"Infraestrutura",'Plano Mestre'!I2:I123,"Concluído")</f>
         <v>0</v>
       </c>
     </row>
@@ -362,11 +362,11 @@
         </is>
       </c>
       <c r="B18" s="2">
-        <f>COUNTIF('Plano Mestre'!B2:B108,"Backend")</f>
+        <f>COUNTIF('Plano Mestre'!B2:B123,"Backend")</f>
         <v>0</v>
       </c>
       <c r="C18" s="2">
-        <f>COUNTIFS('Plano Mestre'!B2:B108,"Backend",'Plano Mestre'!I2:I108,"Concluído")</f>
+        <f>COUNTIFS('Plano Mestre'!B2:B123,"Backend",'Plano Mestre'!I2:I123,"Concluído")</f>
         <v>0</v>
       </c>
     </row>
@@ -377,11 +377,11 @@
         </is>
       </c>
       <c r="B19" s="2">
-        <f>COUNTIF('Plano Mestre'!B2:B108,"Frontend")</f>
+        <f>COUNTIF('Plano Mestre'!B2:B123,"Frontend")</f>
         <v>0</v>
       </c>
       <c r="C19" s="2">
-        <f>COUNTIFS('Plano Mestre'!B2:B108,"Frontend",'Plano Mestre'!I2:I108,"Concluído")</f>
+        <f>COUNTIFS('Plano Mestre'!B2:B123,"Frontend",'Plano Mestre'!I2:I123,"Concluído")</f>
         <v>0</v>
       </c>
     </row>
@@ -392,11 +392,11 @@
         </is>
       </c>
       <c r="B20" s="2">
-        <f>COUNTIF('Plano Mestre'!B2:B108,"Conteúdo")</f>
+        <f>COUNTIF('Plano Mestre'!B2:B123,"Conteúdo")</f>
         <v>0</v>
       </c>
       <c r="C20" s="2">
-        <f>COUNTIFS('Plano Mestre'!B2:B108,"Conteúdo",'Plano Mestre'!I2:I108,"Concluído")</f>
+        <f>COUNTIFS('Plano Mestre'!B2:B123,"Conteúdo",'Plano Mestre'!I2:I123,"Concluído")</f>
         <v>0</v>
       </c>
     </row>
@@ -407,11 +407,11 @@
         </is>
       </c>
       <c r="B21" s="2">
-        <f>COUNTIF('Plano Mestre'!B2:B108,"Qualidade")</f>
+        <f>COUNTIF('Plano Mestre'!B2:B123,"Qualidade")</f>
         <v>0</v>
       </c>
       <c r="C21" s="2">
-        <f>COUNTIFS('Plano Mestre'!B2:B108,"Qualidade",'Plano Mestre'!I2:I108,"Concluído")</f>
+        <f>COUNTIFS('Plano Mestre'!B2:B123,"Qualidade",'Plano Mestre'!I2:I123,"Concluído")</f>
         <v>0</v>
       </c>
     </row>
@@ -422,11 +422,11 @@
         </is>
       </c>
       <c r="B22" s="2">
-        <f>COUNTIF('Plano Mestre'!B2:B108,"Jurídico")</f>
+        <f>COUNTIF('Plano Mestre'!B2:B123,"Jurídico")</f>
         <v>0</v>
       </c>
       <c r="C22" s="2">
-        <f>COUNTIFS('Plano Mestre'!B2:B108,"Jurídico",'Plano Mestre'!I2:I108,"Concluído")</f>
+        <f>COUNTIFS('Plano Mestre'!B2:B123,"Jurídico",'Plano Mestre'!I2:I123,"Concluído")</f>
         <v>0</v>
       </c>
     </row>
@@ -437,11 +437,11 @@
         </is>
       </c>
       <c r="B23" s="2">
-        <f>COUNTIF('Plano Mestre'!B2:B108,"Lançamento")</f>
+        <f>COUNTIF('Plano Mestre'!B2:B123,"Lançamento")</f>
         <v>0</v>
       </c>
       <c r="C23" s="2">
-        <f>COUNTIFS('Plano Mestre'!B2:B108,"Lançamento",'Plano Mestre'!I2:I108,"Concluído")</f>
+        <f>COUNTIFS('Plano Mestre'!B2:B123,"Lançamento",'Plano Mestre'!I2:I123,"Concluído")</f>
         <v>0</v>
       </c>
     </row>
@@ -452,11 +452,11 @@
         </is>
       </c>
       <c r="B24" s="2">
-        <f>COUNTIF('Plano Mestre'!B2:B108,"Pós-lançamento")</f>
+        <f>COUNTIF('Plano Mestre'!B2:B123,"Pós-lançamento")</f>
         <v>0</v>
       </c>
       <c r="C24" s="2">
-        <f>COUNTIFS('Plano Mestre'!B2:B108,"Pós-lançamento",'Plano Mestre'!I2:I108,"Concluído")</f>
+        <f>COUNTIFS('Plano Mestre'!B2:B123,"Pós-lançamento",'Plano Mestre'!I2:I123,"Concluído")</f>
         <v>0</v>
       </c>
     </row>
@@ -795,7 +795,7 @@
       </c>
       <c r="I5" s="0" t="inlineStr">
         <is>
-          <t>Concluído</t>
+          <t>Em andamento</t>
         </is>
       </c>
       <c r="J5" s="0">
@@ -812,11 +812,11 @@
         </is>
       </c>
       <c r="M5" s="3">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="N5" s="0" t="inlineStr">
         <is>
-          <t>Pesquisa consolidada em docs/PESQUISA-CASAIS-BRASILEIROS.md</t>
+          <t>Pesquisa secundária consolidada em docs/PESQUISA-CASAIS-BRASILEIROS.md - síntese das entrevistas e validação das oportunidades dependem da tarefa 3</t>
         </is>
       </c>
     </row>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="N12" s="0" t="inlineStr">
         <is>
-          <t>Linha de base com fases marcos cadência caminho crítico e riscos em docs/CRONOGRAMA-MARCOS-E-CADENCIA.md e Word</t>
+          <t>Linha de base em docs/CRONOGRAMA-MARCOS-E-CADENCIA.md e Word - revisão identificou datas por tarefa e capacidade nominal pendentes de replanejamento com a baseline 112 - datas dos marcos permanecem premissas</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="N13" s="0" t="inlineStr">
         <is>
-          <t>Papéis autoridade matriz RACI e responsáveis das 107 tarefas consolidados em docs/RESPONSAVEIS-E-MATRIZ-RACI.md e Word</t>
+          <t>Estrutura de papéis e RACI documentadas - papéis padrão aplicados às tarefas atuais pelo gerador - nomes técnicos e capacidade ainda a confirmar - documento e Word têm recorte histórico das 107 tarefas iniciais</t>
         </is>
       </c>
     </row>
@@ -1674,7 +1674,7 @@
       </c>
       <c r="N18" s="0" t="inlineStr">
         <is>
-          <t>Posicionamento plataforma de mensagens tom de voz vocabulário aplicações e sistema de slogans consolidados em docs/POSICIONAMENTO-TOM-DE-VOZ-E-SLOGAN.md e Word</t>
+          <t>Posicionamento plataforma de mensagens tom de voz vocabulário aplicações e sistema de slogans consolidados em docs/POSICIONAMENTO-TOM-DE-VOZ-E-SLOGAN.md e Word —  validar com casais e revisar se o naming mudar</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="N19" s="0" t="inlineStr">
         <is>
-          <t>Identidade revisada conforme decisão da fundadora: símbolo 3D original da pasta Identidade visual restaurado no app e wordmark conectadois com dois em dourado</t>
+          <t>Identidade revisada conforme decisão da fundadora: símbolo 3D original da pasta Identidade visual restaurado no app e wordmark conectadois com dois em dourado —  guia Word e preview horizontal atualizados</t>
         </is>
       </c>
     </row>
@@ -1765,7 +1765,7 @@
       </c>
       <c r="E20" s="0" t="inlineStr">
         <is>
-          <t>Mapa de jornada</t>
+          <t>Mapa de jornada e fluxograma visual</t>
         </is>
       </c>
       <c r="F20" s="0" t="inlineStr">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="J20" s="0">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K20" s="0" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
       </c>
       <c r="N20" s="0" t="inlineStr">
         <is>
-          <t>Jornada bilateral em 15 etapas consolidada em docs/JORNADA-COMPLETA-DO-CASAL.md e Word com trilhas de iniciador e convidado emoções fricções métricas blueprint exceções e oportunidades</t>
+          <t>Jornada bilateral em 15 etapas consolidada em docs/JORNADA-COMPLETA-DO-CASAL.md e Word —  fluxograma detalhado em docs/FLUXOGRAMA-JORNADA-COMPLETA-DO-CASAL.md e imagem vetorial pronta para compartilhamento em docs/FLUXOGRAMA-JORNADA-COMPLETA-DO-CASAL.svg —  inclui decisões recuperações regras transversais e marcos mensuráveis —  hipóteses pendentes de validação nas entrevistas</t>
         </is>
       </c>
     </row>
@@ -1851,11 +1851,11 @@
       </c>
       <c r="I21" s="0" t="inlineStr">
         <is>
-          <t>Não iniciado</t>
+          <t>Concluído</t>
         </is>
       </c>
       <c r="J21" s="0">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K21" s="0" t="inlineStr">
         <is>
@@ -1868,11 +1868,11 @@
         </is>
       </c>
       <c r="M21" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N21" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>Arquitetura mobile-first documentada em docs/ARQUITETURA-DE-INFORMACAO.md com mapa geral quatro áreas principais inventário de 29 telas objetos de informação regras de acesso rotas conceituais estados escopo por versão critérios de aceite e plano de validação</t>
         </is>
       </c>
     </row>
@@ -1938,7 +1938,7 @@
       </c>
       <c r="N22" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>Fluxo funcional completo documentado em docs/FLUXO-DE-ONBOARDING.md e diagrama compartilhável em docs/FLUXO-DE-ONBOARDING.svg —  cobre descoberta direta convite recebido consentimento exceções acessibilidade analytics e critérios de aceite —  pendentes protótipo navegável e validação com usuários nas tarefas 29 e 30</t>
         </is>
       </c>
     </row>
@@ -2004,7 +2004,7 @@
       </c>
       <c r="N23" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>Fluxo funcional documentado em docs/FLUXO-DE-CADASTRO-LOGIN-E-RECUPERACAO.md e diagrama em docs/FLUXO-DE-CADASTRO-LOGIN-E-RECUPERACAO.svg —  cobre conta individual contexto de convite validações verificação de e-mail recuperação de senha sessões segurança acessibilidade analytics e lacunas da implementação —  pendentes protótipo e validação nas tarefas 29 e 30</t>
         </is>
       </c>
     </row>
@@ -2115,7 +2115,7 @@
       </c>
       <c r="I25" s="0" t="inlineStr">
         <is>
-          <t>Não iniciado</t>
+          <t>Em andamento</t>
         </is>
       </c>
       <c r="J25" s="0">
@@ -2132,11 +2132,11 @@
         </is>
       </c>
       <c r="M25" s="3">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="N25" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>Desenho em docs/HOME-E-ROTINA-DIARIA.md e protótipo navegável em docs/prototipo-home-rotina.html - 13 estados da home e rotina com perguntas desafios e modo misto - pendentes revisão visual e validação com casais na tarefa 30</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="I26" s="0" t="inlineStr">
         <is>
-          <t>Não iniciado</t>
+          <t>Em andamento</t>
         </is>
       </c>
       <c r="J26" s="0">
@@ -2198,11 +2198,11 @@
         </is>
       </c>
       <c r="M26" s="3">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="N26" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>Desenho em docs/PERGUNTAS-E-REVELACAO-MUTUA.md e protótipo docs/prototipo-perguntas-revelacao.html - discursiva múltipla escolha desafios espera correção pulo retomada e revelação bilateral - verificação de estados automatizada - validação visual e com casais pendentes na tarefa 30</t>
         </is>
       </c>
     </row>
@@ -2247,7 +2247,7 @@
       </c>
       <c r="I27" s="0" t="inlineStr">
         <is>
-          <t>Não iniciado</t>
+          <t>Em andamento</t>
         </is>
       </c>
       <c r="J27" s="0">
@@ -2264,11 +2264,11 @@
         </is>
       </c>
       <c r="M27" s="3">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="N27" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>Desenho em docs/TESTES-E-RESULTADOS.md e protótipo docs/prototipo-testes-resultados.html - formas de afeto e temperamentos experimentais com pausa revisão resultado parcial empate compartilhamento opcional e revogação - verificação de estados em scripts/validate-tests-prototype.mjs - revisão visual editorial especializada e validação com casais pendentes</t>
         </is>
       </c>
     </row>
@@ -2313,7 +2313,7 @@
       </c>
       <c r="I28" s="0" t="inlineStr">
         <is>
-          <t>Não iniciado</t>
+          <t>Em andamento</t>
         </is>
       </c>
       <c r="J28" s="0">
@@ -2330,11 +2330,11 @@
         </is>
       </c>
       <c r="M28" s="3">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="N28" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>Home rotina diária perguntas com revelação e testes com resultados desenhados em protótipos HTML responsivos na pasta docs - demais telas e validação visual completa pendentes</t>
         </is>
       </c>
     </row>
@@ -2379,7 +2379,7 @@
       </c>
       <c r="I29" s="0" t="inlineStr">
         <is>
-          <t>Não iniciado</t>
+          <t>Em andamento</t>
         </is>
       </c>
       <c r="J29" s="0">
@@ -2396,11 +2396,11 @@
         </is>
       </c>
       <c r="M29" s="3">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="N29" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>Tokens em src/assets/brand/brand-tokens.css e guia docs/IDENTIDADE-VISUAL.md existentes - biblioteca de componentes estados acessibilidade e validação visual pendentes</t>
         </is>
       </c>
     </row>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="I30" s="0" t="inlineStr">
         <is>
-          <t>Não iniciado</t>
+          <t>Em andamento</t>
         </is>
       </c>
       <c r="J30" s="0">
@@ -2462,11 +2462,11 @@
         </is>
       </c>
       <c r="M30" s="3">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="N30" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>Protótipos locais da home perguntas e revelação mútua e testes com resultados em docs - inclui perspectivas simuladas rede pausa revisão e compartilhamento opcional de resumo - integração das demais jornadas revisão visual e testes com casais pendentes</t>
         </is>
       </c>
     </row>
@@ -2511,7 +2511,7 @@
       </c>
       <c r="I31" s="0" t="inlineStr">
         <is>
-          <t>Não iniciado</t>
+          <t>Em andamento</t>
         </is>
       </c>
       <c r="J31" s="0">
@@ -2528,11 +2528,11 @@
         </is>
       </c>
       <c r="M31" s="3">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="N31" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>Rodada 0 especializada executada em 05/09/2026 com sete jornadas bilaterais e doze estados responsivos - relatório em docs/TESTE-DE-USABILIDADE-2026-09-05.md - nove achados registrados - validação moderada com casais e métricas humanas ainda pendentes</t>
         </is>
       </c>
     </row>
@@ -2598,7 +2598,7 @@
       </c>
       <c r="N32" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>Correções dos achados UT-01 a UT-09 da rodada 0 pendentes - priorizar entrada em login feedback de falhas integridade do progresso retomada dos testes e alvos de toque antes da rodada com participantes</t>
         </is>
       </c>
     </row>
@@ -2775,7 +2775,7 @@
       </c>
       <c r="I35" s="0" t="inlineStr">
         <is>
-          <t>Não iniciado</t>
+          <t>Concluído</t>
         </is>
       </c>
       <c r="J35" s="0">
@@ -2792,11 +2792,11 @@
         </is>
       </c>
       <c r="M35" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N35" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>Modelo lógico em docs/MODELO-DE-DADOS.md e docs/modelo-de-dados.dbml com 10 entidades e 12 relacionamentos - autenticação partidas respostas desafios e progresso - regras de integridade privacidade e migração documentadas</t>
         </is>
       </c>
     </row>
@@ -2831,7 +2831,7 @@
       </c>
       <c r="G36" s="0" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>34,112</t>
         </is>
       </c>
       <c r="H36" s="0" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="I36" s="0" t="inlineStr">
         <is>
-          <t>Não iniciado</t>
+          <t>Em andamento</t>
         </is>
       </c>
       <c r="J36" s="0">
@@ -2858,11 +2858,11 @@
         </is>
       </c>
       <c r="M36" s="3">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="N36" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>Contrato-base v1 em docs/openapi-v1.json com 21 caminhos 24 operações política de versões erros idempotência concorrência privacidade e migração documentados em docs/CONTRATO-E-VERSIONAMENTO-DA-API.md - validador em scripts/validate-openapi.mjs - estabilização 1.0 depende da decisão 112 threat model 36 LGPD 37 implementação e testes de conformidade</t>
         </is>
       </c>
     </row>
@@ -2907,7 +2907,7 @@
       </c>
       <c r="I37" s="0" t="inlineStr">
         <is>
-          <t>Não iniciado</t>
+          <t>Concluído</t>
         </is>
       </c>
       <c r="J37" s="0">
@@ -2924,11 +2924,11 @@
         </is>
       </c>
       <c r="M37" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N37" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>Baseline STRIDE e OWASP em docs/MODELAGEM-DE-AMEACAS.md com diagrama ativos fronteiras 22 ameaças 29 controles 20 testes gates de piloto e riscos residuais - 13 ameaças críticas 8 altas e 1 média - estado atual não apto para piloto externo - revalidar após tarefas 112-114 PostgreSQL provedores e antes da release candidate</t>
         </is>
       </c>
     </row>
@@ -2973,7 +2973,7 @@
       </c>
       <c r="I38" s="0" t="inlineStr">
         <is>
-          <t>Não iniciado</t>
+          <t>Concluído</t>
         </is>
       </c>
       <c r="J38" s="0">
@@ -2981,20 +2981,20 @@
       </c>
       <c r="K38" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="L38" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="M38" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N38" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>Inventário v1 em docs/INVENTARIO-DE-DADOS-E-BASES-LEGAIS-LGPD.md - 17 grupos e 20 operações com finalidade necessidade bases dos artigos 7 e 11 acesso compartilhamento retenção direitos incidentes e gates - enquadramento sujeito a aprovação jurídica</t>
         </is>
       </c>
     </row>
@@ -3258,7 +3258,7 @@
       </c>
       <c r="N42" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>Provisionar PostgreSQL e migrações executáveis a partir do modelo 34 - validar integridade e concorrência - JSON atual retorna banco vazio ao falhar leitura e não oferece transações</t>
         </is>
       </c>
     </row>
@@ -3953,7 +3953,7 @@
       </c>
       <c r="G53" s="0" t="inlineStr">
         <is>
-          <t>35,41</t>
+          <t>35,41,115</t>
         </is>
       </c>
       <c r="H53" s="0" t="inlineStr">
@@ -3984,7 +3984,7 @@
       </c>
       <c r="N53" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>Catálogo versionado deve servir apenas conteúdo aprovado e publicado com tema nível duração e formato - permitir retirada sem nova versão do app - integrar fonte editorial 115</t>
         </is>
       </c>
     </row>
@@ -4019,7 +4019,7 @@
       </c>
       <c r="G54" s="0" t="inlineStr">
         <is>
-          <t>49,52</t>
+          <t>49,52,111</t>
         </is>
       </c>
       <c r="H54" s="0" t="inlineStr">
@@ -4050,7 +4050,7 @@
       </c>
       <c r="N54" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>Endpoint da pergunta fixa existe - generalizar para partida rodada e autoria por conta com idempotência e correção apenas antes da revelação</t>
         </is>
       </c>
     </row>
@@ -4146,12 +4146,12 @@
       </c>
       <c r="F56" s="0" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="G56" s="0" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>54,111</t>
         </is>
       </c>
       <c r="H56" s="0" t="inlineStr">
@@ -4182,7 +4182,7 @@
       </c>
       <c r="N56" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>Derivar progresso de participação mútua confirmada - substituir contador local inicializado em 3 e incrementado por cliques - releitura e pulo não contam</t>
         </is>
       </c>
     </row>
@@ -4410,7 +4410,7 @@
       </c>
       <c r="F60" s="0" t="inlineStr">
         <is>
-          <t>Baixa</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="G60" s="0" t="inlineStr">
@@ -4446,7 +4446,7 @@
       </c>
       <c r="N60" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>Operação mínima de revisão publicação e retirada com autorização e auditoria - CMS completo não é exigido antes do piloto se existir alternativa segura nas tarefas 52 e 115</t>
         </is>
       </c>
     </row>
@@ -4557,7 +4557,7 @@
       </c>
       <c r="I62" s="0" t="inlineStr">
         <is>
-          <t>Concluído</t>
+          <t>Em andamento</t>
         </is>
       </c>
       <c r="J62" s="0">
@@ -4574,11 +4574,11 @@
         </is>
       </c>
       <c r="M62" s="3">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="N62" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>Três telas implementadas - reaberto na revisão: Já tenho uma conta usa conclusão genérica e abre cadastro - faltam pular e validação do fluxo documentado</t>
         </is>
       </c>
     </row>
@@ -4689,7 +4689,7 @@
       </c>
       <c r="I64" s="0" t="inlineStr">
         <is>
-          <t>Concluído</t>
+          <t>Em andamento</t>
         </is>
       </c>
       <c r="J64" s="0">
@@ -4706,11 +4706,11 @@
         </is>
       </c>
       <c r="M64" s="3">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="N64" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>Criação entrada e espera implementadas - reaberto na revisão: erro de atualização sem mensagem e cópia pode informar sucesso sem clipboard - integração e validação completas pendentes</t>
         </is>
       </c>
     </row>
@@ -4811,7 +4811,7 @@
       </c>
       <c r="G66" s="0" t="inlineStr">
         <is>
-          <t>24,55</t>
+          <t>24,55,116</t>
         </is>
       </c>
       <c r="H66" s="0" t="inlineStr">
@@ -4842,7 +4842,7 @@
       </c>
       <c r="N66" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>Home atual parcial - integrar estados em docs/HOME-E-ROTINA-DIARIA.md com pendências reais e progresso confirmado sem valores demonstrativos</t>
         </is>
       </c>
     </row>
@@ -4877,7 +4877,7 @@
       </c>
       <c r="G67" s="0" t="inlineStr">
         <is>
-          <t>25,52</t>
+          <t>25,52,116</t>
         </is>
       </c>
       <c r="H67" s="0" t="inlineStr">
@@ -4908,7 +4908,7 @@
       </c>
       <c r="N67" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>Jogo local por temas implementado em 109 - níveis leve médio profundo e catálogo remoto ainda pendentes - harmonizar formato e mecânica na tarefa 112</t>
         </is>
       </c>
     </row>
@@ -5537,7 +5537,7 @@
       </c>
       <c r="G77" s="0" t="inlineStr">
         <is>
-          <t>17,60-72</t>
+          <t>17,108,110</t>
         </is>
       </c>
       <c r="H77" s="0" t="inlineStr">
@@ -5568,7 +5568,7 @@
       </c>
       <c r="N77" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>Revisão editorial pode começar pelos lotes candidatos antes de concluir frontend - incluir textos de interface à medida que forem implementados</t>
         </is>
       </c>
     </row>
@@ -5603,7 +5603,7 @@
       </c>
       <c r="G78" s="0" t="inlineStr">
         <is>
-          <t>52,56,57</t>
+          <t>108,110,115</t>
         </is>
       </c>
       <c r="H78" s="0" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="N78" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>Validar lotes e recomendações antes de publicação - distinguir conteúdo candidato de aprovado e seleção mínima de 60 atividades - conteúdo íntimo restrito conforme baseline do piloto</t>
         </is>
       </c>
     </row>
@@ -5766,7 +5766,7 @@
       </c>
       <c r="N80" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>Incluir regras de autenticação autoria duas participações idempotência transições de rodada e progresso - não há suíte versionada identificada nesta revisão</t>
         </is>
       </c>
     </row>
@@ -5867,7 +5867,7 @@
       </c>
       <c r="G82" s="0" t="inlineStr">
         <is>
-          <t>44-59,78</t>
+          <t>44-59,78,111</t>
         </is>
       </c>
       <c r="H82" s="0" t="inlineStr">
@@ -5898,7 +5898,7 @@
       </c>
       <c r="N82" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>Incluir escritas concorrentes falha de persistência retomada isolamento e reenvios - usar dados de teste sem tocar em contas reais</t>
         </is>
       </c>
     </row>
@@ -5933,7 +5933,7 @@
       </c>
       <c r="G83" s="0" t="inlineStr">
         <is>
-          <t>61-70,78</t>
+          <t>61-70,78,116</t>
         </is>
       </c>
       <c r="H83" s="0" t="inlineStr">
@@ -5964,7 +5964,7 @@
       </c>
       <c r="N83" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>Dois contextos autenticados independentes - validar ida e volta da home retomada perguntas desafios pulo e revelação sem vazamento</t>
         </is>
       </c>
     </row>
@@ -6030,7 +6030,7 @@
       </c>
       <c r="N84" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>Aplicar SEC-26 e ST-20 de docs/MODELAGEM-DE-AMEACAS.md - versões fixadas análise de dependências e segredos SBOM revisão de artefato e bloqueio de promoção com vulnerabilidade crítica explorável</t>
         </is>
       </c>
     </row>
@@ -6096,7 +6096,7 @@
       </c>
       <c r="N85" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>Executar casos ST-01 a ST-19 aplicáveis de docs/MODELAGEM-DE-AMEACAS.md com ênfase em BOLA BFLA convite sessão revelação corrida desvinculação logs admin e cache - nenhum vazamento S3 ou S4 e nenhuma ameaça crítica aberta antes do piloto</t>
         </is>
       </c>
     </row>
@@ -6360,7 +6360,7 @@
       </c>
       <c r="N89" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>Usar operações OP-01 a OP-20 e decisões DEC-01 DEC-02 DEC-05 e DEC-08 do inventário LGPD - identificar controlador encarregado operadores transferências finalidades bases prazos direitos e limites da revelação ao parceiro</t>
         </is>
       </c>
     </row>
@@ -6492,7 +6492,7 @@
       </c>
       <c r="N91" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>Implementar CS-01 a CS-05 e DEC-03 DEC-04 DEC-06 DEC-07 DEC-09 e DEC-10 do inventário LGPD - consentimento específico para conteúdo potencialmente sensível revogação exportação exclusão propagação e RIPD antes do piloto</t>
         </is>
       </c>
     </row>
@@ -6558,7 +6558,7 @@
       </c>
       <c r="N92" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>Designar e publicar encarregado ou justificativa aplicável - operacionalizar OP-16 e OP-19 com verificação proporcional prazos RT-01 RT-05 RT-10 fila de operadores e separação de dados do parceiro</t>
         </is>
       </c>
     </row>
@@ -6659,7 +6659,7 @@
       </c>
       <c r="G94" s="0" t="inlineStr">
         <is>
-          <t>41,92</t>
+          <t>41,92,118</t>
         </is>
       </c>
       <c r="H94" s="0" t="inlineStr">
@@ -6690,7 +6690,7 @@
       </c>
       <c r="N94" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>Migração com staging e conferência dos dados legados - backup inicial e restauração comprovada antes de declarar banco pronto</t>
         </is>
       </c>
     </row>
@@ -6822,7 +6822,7 @@
       </c>
       <c r="N96" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>Incluir DEC-11 do inventário LGPD - contato 24x7 avaliação de risco ou dano relevante registro de decisão e comunicação à ANPD e titulares em até 3 dias úteis quando aplicável</t>
         </is>
       </c>
     </row>
@@ -6857,7 +6857,7 @@
       </c>
       <c r="G97" s="0" t="inlineStr">
         <is>
-          <t>87,90,92-95</t>
+          <t>87,90,92-95,77,116,117,119,121,122</t>
         </is>
       </c>
       <c r="H97" s="0" t="inlineStr">
@@ -6888,7 +6888,7 @@
       </c>
       <c r="N97" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>UAT do ciclo bilateral conforme baseline 112 - mecânicas 113 e 114 entram no aceite se mantidas para o piloto - reunir evidências de conteúdo privacidade fornecedores e operação</t>
         </is>
       </c>
     </row>
@@ -7517,7 +7517,7 @@
       </c>
       <c r="G107" s="0" t="inlineStr">
         <is>
-          <t>7,34,35</t>
+          <t>7,34,35,111</t>
         </is>
       </c>
       <c r="H107" s="0" t="inlineStr">
@@ -7527,7 +7527,7 @@
       </c>
       <c r="I107" s="0" t="inlineStr">
         <is>
-          <t>Concluído</t>
+          <t>Em andamento</t>
         </is>
       </c>
       <c r="J107" s="0">
@@ -7544,11 +7544,11 @@
         </is>
       </c>
       <c r="M107" s="3">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="N107" s="0" t="inlineStr">
         <is>
-          <t>Eventos sem conteúdo íntimo e endpoint protegido implementados em server/src/analytics.js</t>
+          <t>Endpoint e agregações implementados - reaberto: eventos financeiros aceitos do cliente reativação não recupera pagantes retenção acumulada rotulada D7 e mode descartado - definir fontes confiáveis e testar métricas</t>
         </is>
       </c>
     </row>
@@ -7593,7 +7593,7 @@
       </c>
       <c r="I108" s="0" t="inlineStr">
         <is>
-          <t>Concluído</t>
+          <t>Em andamento</t>
         </is>
       </c>
       <c r="J108" s="0">
@@ -7610,16 +7610,1006 @@
         </is>
       </c>
       <c r="M108" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="N108" s="0" t="inlineStr">
+        <is>
+          <t>Painel implementado - reaberto para distinguir não instrumentado de zero e esclarecer coortes origem dos dados e limitações - aceite depende da correção e validação da tarefa 106</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="0">
+        <v>108</v>
+      </c>
+      <c r="B109" s="0" t="inlineStr">
+        <is>
+          <t>Conteúdo</t>
+        </is>
+      </c>
+      <c r="C109" s="0" t="inlineStr">
+        <is>
+          <t>Editorial</t>
+        </is>
+      </c>
+      <c r="D109" s="0" t="inlineStr">
+        <is>
+          <t>Produzir banco inicial de perguntas de múltipla escolha</t>
+        </is>
+      </c>
+      <c r="E109" s="0" t="inlineStr">
+        <is>
+          <t>Planilha editorial de perguntas</t>
+        </is>
+      </c>
+      <c r="F109" s="0" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+      <c r="G109" s="0" t="inlineStr">
+        <is>
+          <t>19,17</t>
+        </is>
+      </c>
+      <c r="H109" s="0" t="inlineStr">
+        <is>
+          <t>Pesquisa e Conteúdo</t>
+        </is>
+      </c>
+      <c r="I109" s="0" t="inlineStr">
+        <is>
+          <t>Em andamento</t>
+        </is>
+      </c>
+      <c r="J109" s="0">
+        <v>20</v>
+      </c>
+      <c r="K109" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L109" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M109" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="N109" s="0" t="inlineStr">
+        <is>
+          <t>75 perguntas de múltipla escolha candidatas em Conteúdo/banco-de-perguntas-conectadois.xlsx - produção precede revisão 76 e parecer 77 - pendentes revisão editorial aprovação e seleção do lote do piloto</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="0">
+        <v>109</v>
+      </c>
+      <c r="B110" s="0" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="C110" s="0" t="inlineStr">
+        <is>
+          <t>Jogo</t>
+        </is>
+      </c>
+      <c r="D110" s="0" t="inlineStr">
+        <is>
+          <t>Incluir seleção inicial de temas e formatos</t>
+        </is>
+      </c>
+      <c r="E110" s="0" t="inlineStr">
+        <is>
+          <t>Perguntas discursivas e desafios no mesmo dispositivo</t>
+        </is>
+      </c>
+      <c r="F110" s="0" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="G110" s="0" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="H110" s="0" t="inlineStr">
+        <is>
+          <t>Engenharia Frontend</t>
+        </is>
+      </c>
+      <c r="I110" s="0" t="inlineStr">
+        <is>
+          <t>Concluído</t>
+        </is>
+      </c>
+      <c r="J110" s="0">
+        <v>12</v>
+      </c>
+      <c r="K110" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L110" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M110" s="3">
         <v>1</v>
       </c>
-      <c r="N108" s="0" t="inlineStr">
-        <is>
-          <t>Painel de North Star aquisição ativação engajamento retenção monetização e segurança implementado</t>
+      <c r="N110" s="0" t="inlineStr">
+        <is>
+          <t>Onze temas com dois formatos e modo misto - respostas por jogador e confirmação individual de desafios - pular e reiniciar disponíveis</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="0">
+        <v>110</v>
+      </c>
+      <c r="B111" s="0" t="inlineStr">
+        <is>
+          <t>Conteúdo</t>
+        </is>
+      </c>
+      <c r="C111" s="0" t="inlineStr">
+        <is>
+          <t>Editorial</t>
+        </is>
+      </c>
+      <c r="D111" s="0" t="inlineStr">
+        <is>
+          <t>Ampliar todos os temas com perguntas discursivas e desafios</t>
+        </is>
+      </c>
+      <c r="E111" s="0" t="inlineStr">
+        <is>
+          <t>44 novas atividades no app e banco editorial</t>
+        </is>
+      </c>
+      <c r="F111" s="0" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="G111" s="0" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="H111" s="0" t="inlineStr">
+        <is>
+          <t>Pesquisa e Conteúdo</t>
+        </is>
+      </c>
+      <c r="I111" s="0" t="inlineStr">
+        <is>
+          <t>Em andamento</t>
+        </is>
+      </c>
+      <c r="J111" s="0">
+        <v>8</v>
+      </c>
+      <c r="K111" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L111" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M111" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="N111" s="0" t="inlineStr">
+        <is>
+          <t>Duas perguntas e dois desafios por tema implementados - 22 desafios separados na aba Desafios e perguntas nas abas temáticas - revisão editorial e especializada pendentes antes de publicação</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="0">
+        <v>111</v>
+      </c>
+      <c r="B112" s="0" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="C112" s="0" t="inlineStr">
+        <is>
+          <t>Sessões de jogo</t>
+        </is>
+      </c>
+      <c r="D112" s="0" t="inlineStr">
+        <is>
+          <t>Persistir partidas rodadas e participantes</t>
+        </is>
+      </c>
+      <c r="E112" s="0" t="inlineStr">
+        <is>
+          <t>Serviço de partidas com autorização por casal</t>
+        </is>
+      </c>
+      <c r="F112" s="0" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="G112" s="0" t="inlineStr">
+        <is>
+          <t>34,35,41,49,52</t>
+        </is>
+      </c>
+      <c r="H112" s="0" t="inlineStr">
+        <is>
+          <t>Engenharia Backend</t>
+        </is>
+      </c>
+      <c r="I112" s="0" t="inlineStr">
+        <is>
+          <t>Não iniciado</t>
+        </is>
+      </c>
+      <c r="J112" s="0">
+        <v>16</v>
+      </c>
+      <c r="K112" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L112" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M112" s="3">
+        <v>0</v>
+      </c>
+      <c r="N112" s="0" t="inlineStr">
+        <is>
+          <t>Implementar modelo de partidas e snapshots de conteúdo - integrar respostas e progresso com transações e testes de concorrência</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="0">
+        <v>112</v>
+      </c>
+      <c r="B113" s="0" t="inlineStr">
+        <is>
+          <t>Planejamento</t>
+        </is>
+      </c>
+      <c r="C113" s="0" t="inlineStr">
+        <is>
+          <t>Produto</t>
+        </is>
+      </c>
+      <c r="D113" s="0" t="inlineStr">
+        <is>
+          <t>Reconciliar temas formatos mecânicas e escopo do piloto</t>
+        </is>
+      </c>
+      <c r="E113" s="0" t="inlineStr">
+        <is>
+          <t>Baseline e matriz de rastreabilidade</t>
+        </is>
+      </c>
+      <c r="F113" s="0" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+      <c r="G113" s="0" t="inlineStr">
+        <is>
+          <t>8,10,34</t>
+        </is>
+      </c>
+      <c r="H113" s="0" t="inlineStr">
+        <is>
+          <t>Product Owner — Tatyele Lopes</t>
+        </is>
+      </c>
+      <c r="I113" s="0" t="inlineStr">
+        <is>
+          <t>Não iniciado</t>
+        </is>
+      </c>
+      <c r="J113" s="0">
+        <v>8</v>
+      </c>
+      <c r="K113" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L113" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M113" s="3">
+        <v>0</v>
+      </c>
+      <c r="N113" s="0" t="inlineStr">
+        <is>
+          <t>Conciliar perguntas desafios e misto com resposta guardada adivinhação e coincidências - decidir primeiro piloto e atualizar PRD escopo MoSCoW modelo e cronograma - estimativa preliminar</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="0">
+        <v>113</v>
+      </c>
+      <c r="B114" s="0" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="C114" s="0" t="inlineStr">
+        <is>
+          <t>Jogos</t>
+        </is>
+      </c>
+      <c r="D114" s="0" t="inlineStr">
+        <is>
+          <t>Implementar mecânica bilateral de adivinhação</t>
+        </is>
+      </c>
+      <c r="E114" s="0" t="inlineStr">
+        <is>
+          <t>Fluxo integrado com inversão de papéis</t>
+        </is>
+      </c>
+      <c r="F114" s="0" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="G114" s="0" t="inlineStr">
+        <is>
+          <t>112,35,52,111</t>
+        </is>
+      </c>
+      <c r="H114" s="0" t="inlineStr">
+        <is>
+          <t>Liderança Técnica</t>
+        </is>
+      </c>
+      <c r="I114" s="0" t="inlineStr">
+        <is>
+          <t>Não iniciado</t>
+        </is>
+      </c>
+      <c r="J114" s="0">
+        <v>24</v>
+      </c>
+      <c r="K114" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L114" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M114" s="3">
+        <v>0</v>
+      </c>
+      <c r="N114" s="0" t="inlineStr">
+        <is>
+          <t>Já previsto no escopo MVP - execução condicionada à decisão 112 - incluir modelo de tentativas API interface e testes de autoria - estimativa preliminar</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="0">
+        <v>114</v>
+      </c>
+      <c r="B115" s="0" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="C115" s="0" t="inlineStr">
+        <is>
+          <t>Jogos</t>
+        </is>
+      </c>
+      <c r="D115" s="0" t="inlineStr">
+        <is>
+          <t>Implementar mecânica de escolhas coincidentes</t>
+        </is>
+      </c>
+      <c r="E115" s="0" t="inlineStr">
+        <is>
+          <t>Fluxo de escolhas e fechamento</t>
+        </is>
+      </c>
+      <c r="F115" s="0" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="G115" s="0" t="inlineStr">
+        <is>
+          <t>112,35,52,111</t>
+        </is>
+      </c>
+      <c r="H115" s="0" t="inlineStr">
+        <is>
+          <t>Liderança Técnica</t>
+        </is>
+      </c>
+      <c r="I115" s="0" t="inlineStr">
+        <is>
+          <t>Não iniciado</t>
+        </is>
+      </c>
+      <c r="J115" s="0">
+        <v>24</v>
+      </c>
+      <c r="K115" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L115" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M115" s="3">
+        <v>0</v>
+      </c>
+      <c r="N115" s="0" t="inlineStr">
+        <is>
+          <t>Já previsto no escopo MVP - execução condicionada à decisão 112 - revelar somente coincidências e permitir outra ideia - incluir API interface e testes - estimativa preliminar</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="0">
+        <v>115</v>
+      </c>
+      <c r="B116" s="0" t="inlineStr">
+        <is>
+          <t>Conteúdo</t>
+        </is>
+      </c>
+      <c r="C116" s="0" t="inlineStr">
+        <is>
+          <t>Operação editorial</t>
+        </is>
+      </c>
+      <c r="D116" s="0" t="inlineStr">
+        <is>
+          <t>Unificar fonte editorial e validar importação do catálogo</t>
+        </is>
+      </c>
+      <c r="E116" s="0" t="inlineStr">
+        <is>
+          <t>Conteúdo versionado e validado</t>
+        </is>
+      </c>
+      <c r="F116" s="0" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+      <c r="G116" s="0" t="inlineStr">
+        <is>
+          <t>108,110,112</t>
+        </is>
+      </c>
+      <c r="H116" s="0" t="inlineStr">
+        <is>
+          <t>Pesquisa e Conteúdo</t>
+        </is>
+      </c>
+      <c r="I116" s="0" t="inlineStr">
+        <is>
+          <t>Não iniciado</t>
+        </is>
+      </c>
+      <c r="J116" s="0">
+        <v>16</v>
+      </c>
+      <c r="K116" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L116" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M116" s="3">
+        <v>0</v>
+      </c>
+      <c r="N116" s="0" t="inlineStr">
+        <is>
+          <t>IDs estáveis por atividade tema nível duração formato revisão e publicação - planilhas como visões sem duplicar contagem - validação de schema cobertura e referências - estimativa preliminar</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="0">
+        <v>116</v>
+      </c>
+      <c r="B117" s="0" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="C117" s="0" t="inlineStr">
+        <is>
+          <t>Sessões de jogo</t>
+        </is>
+      </c>
+      <c r="D117" s="0" t="inlineStr">
+        <is>
+          <t>Integrar partidas remotas e retomada em duas contas</t>
+        </is>
+      </c>
+      <c r="E117" s="0" t="inlineStr">
+        <is>
+          <t>Jornada bilateral integrada</t>
+        </is>
+      </c>
+      <c r="F117" s="0" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+      <c r="G117" s="0" t="inlineStr">
+        <is>
+          <t>111,53,54,109</t>
+        </is>
+      </c>
+      <c r="H117" s="0" t="inlineStr">
+        <is>
+          <t>Engenharia Frontend</t>
+        </is>
+      </c>
+      <c r="I117" s="0" t="inlineStr">
+        <is>
+          <t>Não iniciado</t>
+        </is>
+      </c>
+      <c r="J117" s="0">
+        <v>24</v>
+      </c>
+      <c r="K117" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L117" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M117" s="3">
+        <v>0</v>
+      </c>
+      <c r="N117" s="0" t="inlineStr">
+        <is>
+          <t>Distinguir jogo local e remoto - autoria por conta retomada estados de rede pulo e revelação em perguntas desafios e misto - sem confirmar pela outra pessoa - estimativa preliminar</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="0">
+        <v>117</v>
+      </c>
+      <c r="B118" s="0" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="C118" s="0" t="inlineStr">
+        <is>
+          <t>Feedback</t>
+        </is>
+      </c>
+      <c r="D118" s="0" t="inlineStr">
+        <is>
+          <t>Coletar feedback opcional por atividade</t>
+        </is>
+      </c>
+      <c r="E118" s="0" t="inlineStr">
+        <is>
+          <t>Sinais de relevância e desconforto</t>
+        </is>
+      </c>
+      <c r="F118" s="0" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="G118" s="0" t="inlineStr">
+        <is>
+          <t>116,52</t>
+        </is>
+      </c>
+      <c r="H118" s="0" t="inlineStr">
+        <is>
+          <t>Engenharia Frontend</t>
+        </is>
+      </c>
+      <c r="I118" s="0" t="inlineStr">
+        <is>
+          <t>Não iniciado</t>
+        </is>
+      </c>
+      <c r="J118" s="0">
+        <v>12</v>
+      </c>
+      <c r="K118" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L118" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M118" s="3">
+        <v>0</v>
+      </c>
+      <c r="N118" s="0" t="inlineStr">
+        <is>
+          <t>Previsto no piloto - feedback curto opcional sem expor respostas íntimas e triagem editorial agregada - retirada usa operação 52 e 59 - estimativa preliminar</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="0">
+        <v>118</v>
+      </c>
+      <c r="B119" s="0" t="inlineStr">
+        <is>
+          <t>Infraestrutura</t>
+        </is>
+      </c>
+      <c r="C119" s="0" t="inlineStr">
+        <is>
+          <t>Recuperação</t>
+        </is>
+      </c>
+      <c r="D119" s="0" t="inlineStr">
+        <is>
+          <t>Ensaiar restauração de backup e retorno de migração</t>
+        </is>
+      </c>
+      <c r="E119" s="0" t="inlineStr">
+        <is>
+          <t>Evidência de recuperação</t>
+        </is>
+      </c>
+      <c r="F119" s="0" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+      <c r="G119" s="0" t="inlineStr">
+        <is>
+          <t>41,38</t>
+        </is>
+      </c>
+      <c r="H119" s="0" t="inlineStr">
+        <is>
+          <t>DevOps/Plataforma</t>
+        </is>
+      </c>
+      <c r="I119" s="0" t="inlineStr">
+        <is>
+          <t>Não iniciado</t>
+        </is>
+      </c>
+      <c r="J119" s="0">
+        <v>8</v>
+      </c>
+      <c r="K119" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L119" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M119" s="3">
+        <v>0</v>
+      </c>
+      <c r="N119" s="0" t="inlineStr">
+        <is>
+          <t>Executar em ambiente isolado conferir integridade e documentar procedimento antes do piloto - estimativa preliminar</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="0">
+        <v>119</v>
+      </c>
+      <c r="B120" s="0" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="C120" s="0" t="inlineStr">
+        <is>
+          <t>PWA</t>
+        </is>
+      </c>
+      <c r="D120" s="0" t="inlineStr">
+        <is>
+          <t>Configurar instalação PWA e política de cache</t>
+        </is>
+      </c>
+      <c r="E120" s="0" t="inlineStr">
+        <is>
+          <t>Manifest instalação e offline seguro</t>
+        </is>
+      </c>
+      <c r="F120" s="0" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="G120" s="0" t="inlineStr">
+        <is>
+          <t>38,60,73</t>
+        </is>
+      </c>
+      <c r="H120" s="0" t="inlineStr">
+        <is>
+          <t>Engenharia Frontend</t>
+        </is>
+      </c>
+      <c r="I120" s="0" t="inlineStr">
+        <is>
+          <t>Não iniciado</t>
+        </is>
+      </c>
+      <c r="J120" s="0">
+        <v>12</v>
+      </c>
+      <c r="K120" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L120" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M120" s="3">
+        <v>0</v>
+      </c>
+      <c r="N120" s="0" t="inlineStr">
+        <is>
+          <t>Formato PWA previsto no MVP - definir shell público sem cache de respostas privadas e validar atualização saída da conta e experiência offline - estimativa preliminar</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="0">
+        <v>120</v>
+      </c>
+      <c r="B121" s="0" t="inlineStr">
+        <is>
+          <t>Planejamento</t>
+        </is>
+      </c>
+      <c r="C121" s="0" t="inlineStr">
+        <is>
+          <t>Qualidade do plano</t>
+        </is>
+      </c>
+      <c r="D121" s="0" t="inlineStr">
+        <is>
+          <t>Revisar coerência geral entre acompanhamento e entregas</t>
+        </is>
+      </c>
+      <c r="E121" s="0" t="inlineStr">
+        <is>
+          <t>Relatório e plano reconciliado</t>
+        </is>
+      </c>
+      <c r="F121" s="0" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="G121" s="0" t="inlineStr">
+        <is>
+          <t>34,24,109,110</t>
+        </is>
+      </c>
+      <c r="H121" s="0" t="inlineStr">
+        <is>
+          <t>Product Owner — Tatyele Lopes</t>
+        </is>
+      </c>
+      <c r="I121" s="0" t="inlineStr">
+        <is>
+          <t>Concluído</t>
+        </is>
+      </c>
+      <c r="J121" s="0">
+        <v>6</v>
+      </c>
+      <c r="K121" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L121" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M121" s="3">
+        <v>1</v>
+      </c>
+      <c r="N121" s="0" t="inlineStr">
+        <is>
+          <t>Revisão em docs/REVISAO-GERAL-2026-09-04.md - confronto Excel código e documentos build aprovado achados rastreados notas CSV corrigidas e validador scripts/validate-project-plan.ps1</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="0">
+        <v>121</v>
+      </c>
+      <c r="B122" s="0" t="inlineStr">
+        <is>
+          <t>Jurídico</t>
+        </is>
+      </c>
+      <c r="C122" s="0" t="inlineStr">
+        <is>
+          <t>Privacidade</t>
+        </is>
+      </c>
+      <c r="D122" s="0" t="inlineStr">
+        <is>
+          <t>Elaborar RIPD e testes de balanceamento</t>
+        </is>
+      </c>
+      <c r="E122" s="0" t="inlineStr">
+        <is>
+          <t>RIPD e LIAs aprovados</t>
+        </is>
+      </c>
+      <c r="F122" s="0" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+      <c r="G122" s="0" t="inlineStr">
+        <is>
+          <t>36,37,112</t>
+        </is>
+      </c>
+      <c r="H122" s="0" t="inlineStr">
+        <is>
+          <t>Privacidade/Jurídico</t>
+        </is>
+      </c>
+      <c r="I122" s="0" t="inlineStr">
+        <is>
+          <t>Não iniciado</t>
+        </is>
+      </c>
+      <c r="J122" s="0">
+        <v>20</v>
+      </c>
+      <c r="K122" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L122" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M122" s="3">
+        <v>0</v>
+      </c>
+      <c r="N122" s="0" t="inlineStr">
+        <is>
+          <t>Concluir DEC-06 e DEC-10 do inventário LGPD - LIA-01 segurança LIA-02 analytics necessidade proporcionalidade salvaguardas risco residual e aceite formal antes do piloto</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="0">
+        <v>122</v>
+      </c>
+      <c r="B123" s="0" t="inlineStr">
+        <is>
+          <t>Jurídico</t>
+        </is>
+      </c>
+      <c r="C123" s="0" t="inlineStr">
+        <is>
+          <t>Fornecedores</t>
+        </is>
+      </c>
+      <c r="D123" s="0" t="inlineStr">
+        <is>
+          <t>Cadastrar operadores e transferências internacionais</t>
+        </is>
+      </c>
+      <c r="E123" s="0" t="inlineStr">
+        <is>
+          <t>Registro de operadores e contratos</t>
+        </is>
+      </c>
+      <c r="F123" s="0" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+      <c r="G123" s="0" t="inlineStr">
+        <is>
+          <t>37,38,42</t>
+        </is>
+      </c>
+      <c r="H123" s="0" t="inlineStr">
+        <is>
+          <t>Privacidade/Jurídico</t>
+        </is>
+      </c>
+      <c r="I123" s="0" t="inlineStr">
+        <is>
+          <t>Não iniciado</t>
+        </is>
+      </c>
+      <c r="J123" s="0">
+        <v>12</v>
+      </c>
+      <c r="K123" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L123" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M123" s="3">
+        <v>0</v>
+      </c>
+      <c r="N123" s="0" t="inlineStr">
+        <is>
+          <t>Concluir DEC-05 do inventário LGPD - due diligence DPA suboperadores regiões retenção saída incidentes e mecanismo válido da Resolução CD/ANPD 19/2024 antes de dados reais</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N108"/>
+  <autoFilter ref="A1:N123"/>
   <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
 </worksheet>
 </file>
@@ -7834,7 +8824,7 @@
       </c>
       <c r="E6" s="0" t="inlineStr">
         <is>
-          <t>Jornada completa em dois dispositivos e painel funcional</t>
+          <t>Jornada bilateral validada incluindo 111 e 116 e m?tricas 106-107 - 113-114 conforme decis?o 112</t>
         </is>
       </c>
       <c r="F6" s="0" t="inlineStr">
@@ -7869,7 +8859,7 @@
       </c>
       <c r="E7" s="0" t="inlineStr">
         <is>
-          <t>60 atividades com rastreabilidade, teste e revisão</t>
+          <t>60 atividades aprovadas com origem nível teste e revisão - tarefas 77,108,110,115</t>
         </is>
       </c>
       <c r="F7" s="0" t="inlineStr">
@@ -7904,7 +8894,7 @@
       </c>
       <c r="E8" s="0" t="inlineStr">
         <is>
-          <t>QA, segurança, acessibilidade, LGPD e UAT sem bloqueador</t>
+          <t>QA segurança acessibilidade privacidade UAT e restauração 118 sem bloqueador - PWA 119 validada</t>
         </is>
       </c>
       <c r="F8" s="0" t="inlineStr">
@@ -8364,12 +9354,12 @@
       </c>
       <c r="F8" s="0" t="inlineStr">
         <is>
-          <t>Inventário de dados, consentimento, exclusão e revisão jurídica</t>
+          <t>Inventário v1 concluído - resolver DEC-01 a DEC-11 implementar consentimentos e direitos aprovar RIPD LIAs operadores e revisão jurídica</t>
         </is>
       </c>
       <c r="G8" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>Privacidade/Jurídico</t>
         </is>
       </c>
       <c r="H8" s="0" t="inlineStr">
@@ -8504,8 +9494,176 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="0" t="inlineStr">
+        <is>
+          <t>R11</t>
+        </is>
+      </c>
+      <c r="B12" s="0" t="inlineStr">
+        <is>
+          <t>Autorização quebrada expõe dados entre casais</t>
+        </is>
+      </c>
+      <c r="C12" s="0" t="inlineStr">
+        <is>
+          <t>Segurança</t>
+        </is>
+      </c>
+      <c r="D12" s="0" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="E12" s="0" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+      <c r="F12" s="0" t="inlineStr">
+        <is>
+          <t>Autorização por sujeito ação e recurso DTOs mínimos e testes negativos ST-01 a ST-05</t>
+        </is>
+      </c>
+      <c r="G12" s="0" t="inlineStr">
+        <is>
+          <t>Liderança Técnica</t>
+        </is>
+      </c>
+      <c r="H12" s="0" t="inlineStr">
+        <is>
+          <t>Aberto</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="0" t="inlineStr">
+        <is>
+          <t>R12</t>
+        </is>
+      </c>
+      <c r="B13" s="0" t="inlineStr">
+        <is>
+          <t>Convite curto permite sequestro da segunda vaga</t>
+        </is>
+      </c>
+      <c r="C13" s="0" t="inlineStr">
+        <is>
+          <t>Segurança</t>
+        </is>
+      </c>
+      <c r="D13" s="0" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="E13" s="0" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+      <c r="F13" s="0" t="inlineStr">
+        <is>
+          <t>Pelo menos 128 bits hash expiração uso único rate limit e testes ST-06 a ST-08</t>
+        </is>
+      </c>
+      <c r="G13" s="0" t="inlineStr">
+        <is>
+          <t>Liderança Técnica</t>
+        </is>
+      </c>
+      <c r="H13" s="0" t="inlineStr">
+        <is>
+          <t>Aberto</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="0" t="inlineStr">
+        <is>
+          <t>R13</t>
+        </is>
+      </c>
+      <c r="B14" s="0" t="inlineStr">
+        <is>
+          <t>Eventos do cliente adulteram métricas do piloto</t>
+        </is>
+      </c>
+      <c r="C14" s="0" t="inlineStr">
+        <is>
+          <t>Dados</t>
+        </is>
+      </c>
+      <c r="D14" s="0" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="E14" s="0" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="F14" s="0" t="inlineStr">
+        <is>
+          <t>Derivar métricas críticas no servidor rejeitar eventos financeiros e testar replay</t>
+        </is>
+      </c>
+      <c r="G14" s="0" t="inlineStr">
+        <is>
+          <t>Engenharia Backend</t>
+        </is>
+      </c>
+      <c r="H14" s="0" t="inlineStr">
+        <is>
+          <t>Aberto</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="0" t="inlineStr">
+        <is>
+          <t>R14</t>
+        </is>
+      </c>
+      <c r="B15" s="0" t="inlineStr">
+        <is>
+          <t>Cache ou notificação expõe conteúdo íntimo</t>
+        </is>
+      </c>
+      <c r="C15" s="0" t="inlineStr">
+        <is>
+          <t>Privacidade</t>
+        </is>
+      </c>
+      <c r="D15" s="0" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="E15" s="0" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+      <c r="F15" s="0" t="inlineStr">
+        <is>
+          <t>No-store service worker sem S3 ou S4 notificações discretas e teste em aparelho compartilhado</t>
+        </is>
+      </c>
+      <c r="G15" s="0" t="inlineStr">
+        <is>
+          <t>Privacidade/Jurídico</t>
+        </is>
+      </c>
+      <c r="H15" s="0" t="inlineStr">
+        <is>
+          <t>Aberto</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H11"/>
+  <autoFilter ref="A1:H15"/>
   <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
 </worksheet>
 </file>

--- a/Plano de trabalho/acompanhamento-app-do-amor.xlsx
+++ b/Plano de trabalho/acompanhamento-app-do-amor.xlsx
@@ -109,7 +109,7 @@
       </c>
       <c r="B2" s="0" t="inlineStr">
         <is>
-          <t>14/09/2026 18:36</t>
+          <t>16/09/2026 20:36</t>
         </is>
       </c>
       <c r="C2" s="0" t="inlineStr">
@@ -142,7 +142,7 @@
         </is>
       </c>
       <c r="B4" s="2">
-        <f>COUNTA('Plano Mestre'!A2:A138)</f>
+        <f>COUNTA('Plano Mestre'!A2:A140)</f>
         <v>0</v>
       </c>
       <c r="C4" s="0" t="inlineStr">
@@ -158,7 +158,7 @@
         </is>
       </c>
       <c r="B5" s="2">
-        <f>COUNTIF('Plano Mestre'!I2:I138,"Concluído")</f>
+        <f>COUNTIF('Plano Mestre'!I2:I140,"Concluído")</f>
         <v>0</v>
       </c>
       <c r="C5" s="0" t="inlineStr">
@@ -174,7 +174,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIF('Plano Mestre'!I2:I138,"Em andamento")</f>
+        <f>COUNTIF('Plano Mestre'!I2:I140,"Em andamento")</f>
         <v>0</v>
       </c>
       <c r="C6" s="0" t="inlineStr">
@@ -190,7 +190,7 @@
         </is>
       </c>
       <c r="B7" s="2">
-        <f>COUNTIF('Plano Mestre'!I2:I138,"Não iniciado")</f>
+        <f>COUNTIF('Plano Mestre'!I2:I140,"Não iniciado")</f>
         <v>0</v>
       </c>
       <c r="C7" s="0" t="inlineStr">
@@ -206,7 +206,7 @@
         </is>
       </c>
       <c r="B8" s="3">
-        <f>AVERAGE('Plano Mestre'!M2:M138)</f>
+        <f>AVERAGE('Plano Mestre'!M2:M140)</f>
         <v>0</v>
       </c>
       <c r="C8" s="0" t="inlineStr">
@@ -222,7 +222,7 @@
         </is>
       </c>
       <c r="B9" s="2">
-        <f>SUM('Plano Mestre'!J2:J138)</f>
+        <f>SUM('Plano Mestre'!J2:J140)</f>
         <v>0</v>
       </c>
       <c r="C9" s="0" t="inlineStr">
@@ -272,11 +272,11 @@
         </is>
       </c>
       <c r="B12" s="2">
-        <f>COUNTIF('Plano Mestre'!B2:B138,"Descoberta")</f>
+        <f>COUNTIF('Plano Mestre'!B2:B140,"Descoberta")</f>
         <v>0</v>
       </c>
       <c r="C12" s="2">
-        <f>COUNTIFS('Plano Mestre'!B2:B138,"Descoberta",'Plano Mestre'!I2:I138,"Concluído")</f>
+        <f>COUNTIFS('Plano Mestre'!B2:B140,"Descoberta",'Plano Mestre'!I2:I140,"Concluído")</f>
         <v>0</v>
       </c>
     </row>
@@ -287,11 +287,11 @@
         </is>
       </c>
       <c r="B13" s="2">
-        <f>COUNTIF('Plano Mestre'!B2:B138,"Planejamento")</f>
+        <f>COUNTIF('Plano Mestre'!B2:B140,"Planejamento")</f>
         <v>0</v>
       </c>
       <c r="C13" s="2">
-        <f>COUNTIFS('Plano Mestre'!B2:B138,"Planejamento",'Plano Mestre'!I2:I138,"Concluído")</f>
+        <f>COUNTIFS('Plano Mestre'!B2:B140,"Planejamento",'Plano Mestre'!I2:I140,"Concluído")</f>
         <v>0</v>
       </c>
     </row>
@@ -302,11 +302,11 @@
         </is>
       </c>
       <c r="B14" s="2">
-        <f>COUNTIF('Plano Mestre'!B2:B138,"Marca")</f>
+        <f>COUNTIF('Plano Mestre'!B2:B140,"Marca")</f>
         <v>0</v>
       </c>
       <c r="C14" s="2">
-        <f>COUNTIFS('Plano Mestre'!B2:B138,"Marca",'Plano Mestre'!I2:I138,"Concluído")</f>
+        <f>COUNTIFS('Plano Mestre'!B2:B140,"Marca",'Plano Mestre'!I2:I140,"Concluído")</f>
         <v>0</v>
       </c>
     </row>
@@ -317,11 +317,11 @@
         </is>
       </c>
       <c r="B15" s="2">
-        <f>COUNTIF('Plano Mestre'!B2:B138,"UX/UI")</f>
+        <f>COUNTIF('Plano Mestre'!B2:B140,"UX/UI")</f>
         <v>0</v>
       </c>
       <c r="C15" s="2">
-        <f>COUNTIFS('Plano Mestre'!B2:B138,"UX/UI",'Plano Mestre'!I2:I138,"Concluído")</f>
+        <f>COUNTIFS('Plano Mestre'!B2:B140,"UX/UI",'Plano Mestre'!I2:I140,"Concluído")</f>
         <v>0</v>
       </c>
     </row>
@@ -332,11 +332,11 @@
         </is>
       </c>
       <c r="B16" s="2">
-        <f>COUNTIF('Plano Mestre'!B2:B138,"Arquitetura")</f>
+        <f>COUNTIF('Plano Mestre'!B2:B140,"Arquitetura")</f>
         <v>0</v>
       </c>
       <c r="C16" s="2">
-        <f>COUNTIFS('Plano Mestre'!B2:B138,"Arquitetura",'Plano Mestre'!I2:I138,"Concluído")</f>
+        <f>COUNTIFS('Plano Mestre'!B2:B140,"Arquitetura",'Plano Mestre'!I2:I140,"Concluído")</f>
         <v>0</v>
       </c>
     </row>
@@ -347,11 +347,11 @@
         </is>
       </c>
       <c r="B17" s="2">
-        <f>COUNTIF('Plano Mestre'!B2:B138,"Infraestrutura")</f>
+        <f>COUNTIF('Plano Mestre'!B2:B140,"Infraestrutura")</f>
         <v>0</v>
       </c>
       <c r="C17" s="2">
-        <f>COUNTIFS('Plano Mestre'!B2:B138,"Infraestrutura",'Plano Mestre'!I2:I138,"Concluído")</f>
+        <f>COUNTIFS('Plano Mestre'!B2:B140,"Infraestrutura",'Plano Mestre'!I2:I140,"Concluído")</f>
         <v>0</v>
       </c>
     </row>
@@ -362,11 +362,11 @@
         </is>
       </c>
       <c r="B18" s="2">
-        <f>COUNTIF('Plano Mestre'!B2:B138,"Backend")</f>
+        <f>COUNTIF('Plano Mestre'!B2:B140,"Backend")</f>
         <v>0</v>
       </c>
       <c r="C18" s="2">
-        <f>COUNTIFS('Plano Mestre'!B2:B138,"Backend",'Plano Mestre'!I2:I138,"Concluído")</f>
+        <f>COUNTIFS('Plano Mestre'!B2:B140,"Backend",'Plano Mestre'!I2:I140,"Concluído")</f>
         <v>0</v>
       </c>
     </row>
@@ -377,11 +377,11 @@
         </is>
       </c>
       <c r="B19" s="2">
-        <f>COUNTIF('Plano Mestre'!B2:B138,"Frontend")</f>
+        <f>COUNTIF('Plano Mestre'!B2:B140,"Frontend")</f>
         <v>0</v>
       </c>
       <c r="C19" s="2">
-        <f>COUNTIFS('Plano Mestre'!B2:B138,"Frontend",'Plano Mestre'!I2:I138,"Concluído")</f>
+        <f>COUNTIFS('Plano Mestre'!B2:B140,"Frontend",'Plano Mestre'!I2:I140,"Concluído")</f>
         <v>0</v>
       </c>
     </row>
@@ -392,11 +392,11 @@
         </is>
       </c>
       <c r="B20" s="2">
-        <f>COUNTIF('Plano Mestre'!B2:B138,"Conteúdo")</f>
+        <f>COUNTIF('Plano Mestre'!B2:B140,"Conteúdo")</f>
         <v>0</v>
       </c>
       <c r="C20" s="2">
-        <f>COUNTIFS('Plano Mestre'!B2:B138,"Conteúdo",'Plano Mestre'!I2:I138,"Concluído")</f>
+        <f>COUNTIFS('Plano Mestre'!B2:B140,"Conteúdo",'Plano Mestre'!I2:I140,"Concluído")</f>
         <v>0</v>
       </c>
     </row>
@@ -407,11 +407,11 @@
         </is>
       </c>
       <c r="B21" s="2">
-        <f>COUNTIF('Plano Mestre'!B2:B138,"Qualidade")</f>
+        <f>COUNTIF('Plano Mestre'!B2:B140,"Qualidade")</f>
         <v>0</v>
       </c>
       <c r="C21" s="2">
-        <f>COUNTIFS('Plano Mestre'!B2:B138,"Qualidade",'Plano Mestre'!I2:I138,"Concluído")</f>
+        <f>COUNTIFS('Plano Mestre'!B2:B140,"Qualidade",'Plano Mestre'!I2:I140,"Concluído")</f>
         <v>0</v>
       </c>
     </row>
@@ -422,11 +422,11 @@
         </is>
       </c>
       <c r="B22" s="2">
-        <f>COUNTIF('Plano Mestre'!B2:B138,"Jurídico")</f>
+        <f>COUNTIF('Plano Mestre'!B2:B140,"Jurídico")</f>
         <v>0</v>
       </c>
       <c r="C22" s="2">
-        <f>COUNTIFS('Plano Mestre'!B2:B138,"Jurídico",'Plano Mestre'!I2:I138,"Concluído")</f>
+        <f>COUNTIFS('Plano Mestre'!B2:B140,"Jurídico",'Plano Mestre'!I2:I140,"Concluído")</f>
         <v>0</v>
       </c>
     </row>
@@ -437,11 +437,11 @@
         </is>
       </c>
       <c r="B23" s="2">
-        <f>COUNTIF('Plano Mestre'!B2:B138,"Lançamento")</f>
+        <f>COUNTIF('Plano Mestre'!B2:B140,"Lançamento")</f>
         <v>0</v>
       </c>
       <c r="C23" s="2">
-        <f>COUNTIFS('Plano Mestre'!B2:B138,"Lançamento",'Plano Mestre'!I2:I138,"Concluído")</f>
+        <f>COUNTIFS('Plano Mestre'!B2:B140,"Lançamento",'Plano Mestre'!I2:I140,"Concluído")</f>
         <v>0</v>
       </c>
     </row>
@@ -452,11 +452,11 @@
         </is>
       </c>
       <c r="B24" s="2">
-        <f>COUNTIF('Plano Mestre'!B2:B138,"Pós-lançamento")</f>
+        <f>COUNTIF('Plano Mestre'!B2:B140,"Pós-lançamento")</f>
         <v>0</v>
       </c>
       <c r="C24" s="2">
-        <f>COUNTIFS('Plano Mestre'!B2:B138,"Pós-lançamento",'Plano Mestre'!I2:I138,"Concluído")</f>
+        <f>COUNTIFS('Plano Mestre'!B2:B140,"Pós-lançamento",'Plano Mestre'!I2:I140,"Concluído")</f>
         <v>0</v>
       </c>
     </row>
@@ -467,11 +467,11 @@
         </is>
       </c>
       <c r="B25" s="2">
-        <f>COUNTIF('Plano Mestre'!B2:B138,"MPV de teste")</f>
+        <f>COUNTIF('Plano Mestre'!B2:B140,"MPV de teste")</f>
         <v>0</v>
       </c>
       <c r="C25" s="2">
-        <f>COUNTIFS('Plano Mestre'!B2:B138,"MPV de teste",'Plano Mestre'!I2:I138,"Concluído")</f>
+        <f>COUNTIFS('Plano Mestre'!B2:B140,"MPV de teste",'Plano Mestre'!I2:I140,"Concluído")</f>
         <v>0</v>
       </c>
     </row>
@@ -3384,7 +3384,7 @@
       </c>
       <c r="I44" s="0" t="inlineStr">
         <is>
-          <t>Não iniciado</t>
+          <t>Em andamento</t>
         </is>
       </c>
       <c r="J44" s="0">
@@ -3401,11 +3401,11 @@
         </is>
       </c>
       <c r="M44" s="3">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="N44" s="0" t="inlineStr">
         <is>
-          <t>Separar logs métricas e alertas por ambiente e versão conforme docs/AMBIENTES.md - implementar sondas de saúde e prontidão sem dados privados - testar alertas de indisponibilidade erros banco backup e capacidade sem conteúdo íntimo ou segredos</t>
+          <t>Sonda mínima GET /api/health implementada sem dados privados em 16/09/2026 - ainda separar logs métricas e alertas por ambiente e versão implementar prontidão do armazenamento e testar alertas de indisponibilidade erros banco backup e capacidade sem conteúdo íntimo ou segredos</t>
         </is>
       </c>
     </row>
@@ -8883,7 +8883,7 @@
       </c>
       <c r="N127" s="0" t="inlineStr">
         <is>
-          <t>Fluxo aprovado em docs/FLUXO-MPV.md com seis estados entrada direta dois jogos de três rodadas feedback de três sinais exceções e critérios de aceite — concluído antecipadamente em 12/09/2026</t>
+          <t>Fluxo aprovado em docs/FLUXO-MPV.md com seis estados entrada direta dois jogos de três rodadas três sinais e sugestão opcional exceções e critérios de aceite — atualizado em 16/09/2026</t>
         </is>
       </c>
     </row>
@@ -9213,7 +9213,7 @@
       </c>
       <c r="N132" s="0" t="inlineStr">
         <is>
-          <t>Feedback binário compartilhado implementado nos dois jogos com registro local somente do jogo concluído, clareza, descoberta ou conexão e intenção de jogar novamente, sem conteúdo das rodadas — concluído antecipadamente em 12/09/2026</t>
+          <t>Feedback binário compartilhado implementado nos dois jogos e integrado ao registro central do jogo concluído clareza descoberta ou conexão e intenção de jogar novamente sem conteúdo das rodadas — concluído antecipadamente em 12/09/2026 e integrado em 16/09/2026</t>
         </is>
       </c>
     </row>
@@ -9380,7 +9380,7 @@
       </c>
       <c r="G135" s="0" t="inlineStr">
         <is>
-          <t>132,133</t>
+          <t>132,133,138,139</t>
         </is>
       </c>
       <c r="H135" s="0" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="N135" s="0" t="inlineStr">
         <is>
-          <t>Validador móvel já cobre caminhos felizes pulo limpeza de escolha reinício e cancelamento de saída — iniciar aceite formal após concluir 132 e 133 e confirmar troca entre jogos sem estado residual</t>
+          <t>Validadores cobrem caminhos felizes pulo limpeza de escolha reinício cancelamento de saída sugestão opcional persistência exportação e serviço integrado de produção — iniciar aceite formal após concluir 132 e 133 e confirmar troca entre jogos sem estado residual</t>
         </is>
       </c>
     </row>
@@ -9456,7 +9456,7 @@
       </c>
       <c r="I136" s="0" t="inlineStr">
         <is>
-          <t>Não iniciado</t>
+          <t>Em andamento</t>
         </is>
       </c>
       <c r="J136" s="0">
@@ -9464,20 +9464,20 @@
       </c>
       <c r="K136" s="0" t="inlineStr">
         <is>
+          <t>16/09/2026</t>
+        </is>
+      </c>
+      <c r="L136" s="0" t="inlineStr">
+        <is>
           <t>22/09/2026</t>
         </is>
       </c>
-      <c r="L136" s="0" t="inlineStr">
-        <is>
-          <t>22/09/2026</t>
-        </is>
-      </c>
       <c r="M136" s="3">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="N136" s="0" t="inlineStr">
         <is>
-          <t>Publicação temporária sem cadastro dados pessoais analytics de terceiros ou indexação pública</t>
+          <t>Serviço único preparado e Blueprint do Render definido na região Virginia com plano pago disco persistente de 1 GB sonda de saúde CORS restrito bloqueio de indexação e segredo gerado — aguardando autenticação do workspace deploy HTTPS e validação do endereço final</t>
         </is>
       </c>
     </row>
@@ -9543,7 +9543,7 @@
       </c>
       <c r="N137" s="0" t="inlineStr">
         <is>
-          <t>Cada casal joga sem mediação e envia apenas os três sinais do produto — não há entrevistas nem etapa de pesquisa dentro do MPV</t>
+          <t>Cada casal joga sem mediação e envia os três sinais do produto com sugestão de melhoria opcional — não há entrevistas nem etapa de pesquisa dentro do MPV</t>
         </is>
       </c>
     </row>
@@ -9613,8 +9613,140 @@
         </is>
       </c>
     </row>
+    <row r="139">
+      <c r="A139" s="0">
+        <v>138</v>
+      </c>
+      <c r="B139" s="0" t="inlineStr">
+        <is>
+          <t>MPV de teste</t>
+        </is>
+      </c>
+      <c r="C139" s="0" t="inlineStr">
+        <is>
+          <t>Feedback</t>
+        </is>
+      </c>
+      <c r="D139" s="0" t="inlineStr">
+        <is>
+          <t>Adicionar sugestões abertas opcionais ao feedback</t>
+        </is>
+      </c>
+      <c r="E139" s="0" t="inlineStr">
+        <is>
+          <t>Campo de sugestões funcional</t>
+        </is>
+      </c>
+      <c r="F139" s="0" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="G139" s="0" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="H139" s="0" t="inlineStr">
+        <is>
+          <t>Engenharia Frontend</t>
+        </is>
+      </c>
+      <c r="I139" s="0" t="inlineStr">
+        <is>
+          <t>Concluído</t>
+        </is>
+      </c>
+      <c r="J139" s="0">
+        <v>3</v>
+      </c>
+      <c r="K139" s="0" t="inlineStr">
+        <is>
+          <t>16/09/2026</t>
+        </is>
+      </c>
+      <c r="L139" s="0" t="inlineStr">
+        <is>
+          <t>16/09/2026</t>
+        </is>
+      </c>
+      <c r="M139" s="3">
+        <v>1</v>
+      </c>
+      <c r="N139" s="0" t="inlineStr">
+        <is>
+          <t>Campo opcional de até 500 caracteres implementado com orientação para não inserir dados pessoais e cobertura na matriz móvel — concluído em 16/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="0">
+        <v>139</v>
+      </c>
+      <c r="B140" s="0" t="inlineStr">
+        <is>
+          <t>MPV de teste</t>
+        </is>
+      </c>
+      <c r="C140" s="0" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="D140" s="0" t="inlineStr">
+        <is>
+          <t>Centralizar feedback e disponibilizar exportação controlada</t>
+        </is>
+      </c>
+      <c r="E140" s="0" t="inlineStr">
+        <is>
+          <t>API e CSV protegidos</t>
+        </is>
+      </c>
+      <c r="F140" s="0" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+      <c r="G140" s="0" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="H140" s="0" t="inlineStr">
+        <is>
+          <t>Engenharia Backend</t>
+        </is>
+      </c>
+      <c r="I140" s="0" t="inlineStr">
+        <is>
+          <t>Concluído</t>
+        </is>
+      </c>
+      <c r="J140" s="0">
+        <v>6</v>
+      </c>
+      <c r="K140" s="0" t="inlineStr">
+        <is>
+          <t>16/09/2026</t>
+        </is>
+      </c>
+      <c r="L140" s="0" t="inlineStr">
+        <is>
+          <t>16/09/2026</t>
+        </is>
+      </c>
+      <c r="M140" s="3">
+        <v>1</v>
+      </c>
+      <c r="N140" s="0" t="inlineStr">
+        <is>
+          <t>POST anônimo com validação idempotência controle de origem rate limit e retenção no JSON além de exportação CSV protegida por token e testes automatizados — concluído em 16/09/2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N138"/>
+  <autoFilter ref="A1:N140"/>
   <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
 </worksheet>
 </file>
@@ -11017,8 +11149,50 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" s="0" t="inlineStr">
+        <is>
+          <t>MR06</t>
+        </is>
+      </c>
+      <c r="B21" s="0" t="inlineStr">
+        <is>
+          <t>Sugestão aberta conter nomes contatos ou detalhes pessoais</t>
+        </is>
+      </c>
+      <c r="C21" s="0" t="inlineStr">
+        <is>
+          <t>Privacidade</t>
+        </is>
+      </c>
+      <c r="D21" s="0" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="E21" s="0" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="F21" s="0" t="inlineStr">
+        <is>
+          <t>Limitar a 500 caracteres orientar a não inserir dados pessoais restringir a exportação e aplicar retenção de 90 dias</t>
+        </is>
+      </c>
+      <c r="G21" s="0" t="inlineStr">
+        <is>
+          <t>Privacidade/Jurídico</t>
+        </is>
+      </c>
+      <c r="H21" s="0" t="inlineStr">
+        <is>
+          <t>Aberto</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H20"/>
+  <autoFilter ref="A1:H21"/>
   <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
 </worksheet>
 </file>

--- a/Plano de trabalho/acompanhamento-app-do-amor.xlsx
+++ b/Plano de trabalho/acompanhamento-app-do-amor.xlsx
@@ -109,7 +109,7 @@
       </c>
       <c r="B2" s="0" t="inlineStr">
         <is>
-          <t>16/09/2026 20:36</t>
+          <t>16/09/2026 20:39</t>
         </is>
       </c>
       <c r="C2" s="0" t="inlineStr">
@@ -9477,7 +9477,7 @@
       </c>
       <c r="N136" s="0" t="inlineStr">
         <is>
-          <t>Serviço único preparado e Blueprint do Render definido na região Virginia com plano pago disco persistente de 1 GB sonda de saúde CORS restrito bloqueio de indexação e segredo gerado — aguardando autenticação do workspace deploy HTTPS e validação do endereço final</t>
+          <t>Serviço único preparado e Blueprint do Render definido na região Virginia com plano pago disco persistente de 1 GB sonda de saúde CORS restrito bloqueio de indexação e segredo gerado — workspace autenticado e aguardando cadastro de pagamento deploy HTTPS e validação do endereço final</t>
         </is>
       </c>
     </row>

--- a/Plano de trabalho/acompanhamento-app-do-amor.xlsx
+++ b/Plano de trabalho/acompanhamento-app-do-amor.xlsx
@@ -109,7 +109,7 @@
       </c>
       <c r="B2" s="0" t="inlineStr">
         <is>
-          <t>16/09/2026 20:39</t>
+          <t>16/09/2026 20:47</t>
         </is>
       </c>
       <c r="C2" s="0" t="inlineStr">
@@ -2943,7 +2943,7 @@
       </c>
       <c r="N37" s="0" t="inlineStr">
         <is>
-          <t>Baseline STRIDE e OWASP em docs/MODELAGEM-DE-AMEACAS.md com diagrama ativos fronteiras 22 ameaças 29 controles 20 testes gates de piloto e riscos residuais - 13 ameaças críticas 8 altas e 1 média - estado atual não apto para piloto externo - revalidar após tarefas 112-114 PostgreSQL provedores e antes da release candidate</t>
+          <t>Baseline STRIDE e OWASP em docs/MODELAGEM-DE-AMEACAS.md com diagrama ativos fronteiras 23 ameaças 30 controles 21 testes gates de piloto e riscos residuais - 13 ameaças críticas 9 altas e 1 média - estado atual não apto para piloto externo - revalidar após tarefas 112-114 PostgreSQL provedores e antes da release candidate</t>
         </is>
       </c>
     </row>
@@ -3252,7 +3252,7 @@
       </c>
       <c r="I42" s="0" t="inlineStr">
         <is>
-          <t>Não iniciado</t>
+          <t>Em andamento</t>
         </is>
       </c>
       <c r="J42" s="0">
@@ -3269,11 +3269,11 @@
         </is>
       </c>
       <c r="M42" s="3">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="N42" s="0" t="inlineStr">
         <is>
-          <t>Provisionar PostgreSQL local staging e production com identidades distintas mesma versão principal e migrações conforme docs/AMBIENTES.md - implementar DATABASE_URL validar conexão integridade e concorrência - JSON atual sem transações fica restrito ao protótipo local</t>
+          <t>Adaptador DATABASE_URL e schema idempotente implementados para o feedback do MPV em 16/09/2026 com PostgreSQL gratuito temporário no Render - ainda provisionar local staging e production definitivos com identidades distintas migrações integridade concorrência e migração dos demais dados</t>
         </is>
       </c>
     </row>
@@ -9477,7 +9477,7 @@
       </c>
       <c r="N136" s="0" t="inlineStr">
         <is>
-          <t>Serviço único preparado e Blueprint do Render definido na região Virginia com plano pago disco persistente de 1 GB sonda de saúde CORS restrito bloqueio de indexação e segredo gerado — workspace autenticado e aguardando cadastro de pagamento deploy HTTPS e validação do endereço final</t>
+          <t>Blueprint gratuito do Render definido na região Virginia com Web Service PostgreSQL de 1 GB sonda de saúde CORS restrito bloqueio de indexação e segredo gerado — banco expira em 30 dias sem backup e aguardam deploy HTTPS exportação de teste e validação do endereço final</t>
         </is>
       </c>
     </row>
@@ -9741,7 +9741,7 @@
       </c>
       <c r="N140" s="0" t="inlineStr">
         <is>
-          <t>POST anônimo com validação idempotência controle de origem rate limit e retenção no JSON além de exportação CSV protegida por token e testes automatizados — concluído em 16/09/2026</t>
+          <t>POST anônimo com validação idempotência controle de origem rate limit armazenamento PostgreSQL remoto com fallback JSON local e exportação CSV protegida por token — concluído em 16/09/2026</t>
         </is>
       </c>
     </row>
@@ -10589,7 +10589,7 @@
       </c>
       <c r="F7" s="0" t="inlineStr">
         <is>
-          <t>Migrar para PostgreSQL antes da publicação</t>
+          <t>Feedback remoto já usa PostgreSQL temporário - migrar os demais dados e provisionar banco definitivo antes da publicação ampla</t>
         </is>
       </c>
       <c r="G7" s="0" t="inlineStr">
@@ -11177,7 +11177,7 @@
       </c>
       <c r="F21" s="0" t="inlineStr">
         <is>
-          <t>Limitar a 500 caracteres orientar a não inserir dados pessoais restringir a exportação e aplicar retenção de 90 dias</t>
+          <t>Limitar a 500 caracteres orientar a não inserir dados pessoais restringir a exportação e excluir a base gratuita em até 30 dias</t>
         </is>
       </c>
       <c r="G21" s="0" t="inlineStr">

--- a/Plano de trabalho/acompanhamento-app-do-amor.xlsx
+++ b/Plano de trabalho/acompanhamento-app-do-amor.xlsx
@@ -109,7 +109,7 @@
       </c>
       <c r="B2" s="0" t="inlineStr">
         <is>
-          <t>16/09/2026 20:47</t>
+          <t>16/09/2026 20:55</t>
         </is>
       </c>
       <c r="C2" s="0" t="inlineStr">
@@ -9456,7 +9456,7 @@
       </c>
       <c r="I136" s="0" t="inlineStr">
         <is>
-          <t>Em andamento</t>
+          <t>Concluído</t>
         </is>
       </c>
       <c r="J136" s="0">
@@ -9469,15 +9469,15 @@
       </c>
       <c r="L136" s="0" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="M136" s="3">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="N136" s="0" t="inlineStr">
         <is>
-          <t>Blueprint gratuito do Render definido na região Virginia com Web Service PostgreSQL de 1 GB sonda de saúde CORS restrito bloqueio de indexação e segredo gerado — banco expira em 30 dias sem backup e aguardam deploy HTTPS exportação de teste e validação do endereço final</t>
+          <t>Demonstração HTTPS publicada no Render gratuito com Web Service PostgreSQL de 1 GB sonda de saúde CORS restrito bloqueio de indexação e segredo operacional — envio persistência e exportação validados base sintética removida e banco expira em 16/10/2026 sem backup — passagem física Android e iPhone continua na tarefa 132 antes de ampliar o teste</t>
         </is>
       </c>
     </row>

--- a/Plano de trabalho/acompanhamento-app-do-amor.xlsx
+++ b/Plano de trabalho/acompanhamento-app-do-amor.xlsx
@@ -109,7 +109,7 @@
       </c>
       <c r="B2" s="0" t="inlineStr">
         <is>
-          <t>16/09/2026 20:55</t>
+          <t>16/09/2026 21:01</t>
         </is>
       </c>
       <c r="C2" s="0" t="inlineStr">
@@ -9279,7 +9279,7 @@
       </c>
       <c r="N133" s="0" t="inlineStr">
         <is>
-          <t>Matriz Chromium revalidada em 14/09/2026 com cinco viewports e 95 estados em docs/VALIDACAO-MOBILE-MPV-2026-09-14.md — MOB-01 a MOB-03 resolvidos, sem overflow ou exposição do nome do aplicativo e com toque pulo confirmação rotação fluxos completos e reinício aprovados — pendente somente passagem física em Chrome Android e Safari iOS</t>
+          <t>Matriz Chromium revalidada em 14/09/2026 com cinco viewports e 95 estados — roteiro físico incorporado em docs/VALIDACAO-MOBILE-MPV-2026-09-14.md com 12 verificações por plataforma identificação dos aparelhos evidências feedbacks técnicos e critério de aceite — pendente executar e registrar aprovação em Chrome Android e Safari iOS físicos e remover os dois feedbacks técnicos</t>
         </is>
       </c>
     </row>

--- a/Plano de trabalho/acompanhamento-app-do-amor.xlsx
+++ b/Plano de trabalho/acompanhamento-app-do-amor.xlsx
@@ -109,7 +109,7 @@
       </c>
       <c r="B2" s="0" t="inlineStr">
         <is>
-          <t>16/09/2026 21:01</t>
+          <t>16/09/2026 21:11</t>
         </is>
       </c>
       <c r="C2" s="0" t="inlineStr">
@@ -9258,7 +9258,7 @@
       </c>
       <c r="I133" s="0" t="inlineStr">
         <is>
-          <t>Em andamento</t>
+          <t>Concluído</t>
         </is>
       </c>
       <c r="J133" s="0">
@@ -9266,20 +9266,20 @@
       </c>
       <c r="K133" s="0" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L133" s="0" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="M133" s="3">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="N133" s="0" t="inlineStr">
         <is>
-          <t>Matriz Chromium revalidada em 14/09/2026 com cinco viewports e 95 estados — roteiro físico incorporado em docs/VALIDACAO-MOBILE-MPV-2026-09-14.md com 12 verificações por plataforma identificação dos aparelhos evidências feedbacks técnicos e critério de aceite — pendente executar e registrar aprovação em Chrome Android e Safari iOS físicos e remover os dois feedbacks técnicos</t>
+          <t>Aprovado com ressalva para o escopo controlado no Chrome após passagem física confirmada pela Product Owner feedback real com três sinais positivos saúde exportação persistência dois jogos e 95 estados móveis revalidados — registro técnico removido e base vazia — modelo sistema e versão não informados — Safari adiado por decisão da Product Owner e explicitamente não validado</t>
         </is>
       </c>
     </row>
@@ -9390,7 +9390,7 @@
       </c>
       <c r="I135" s="0" t="inlineStr">
         <is>
-          <t>Não iniciado</t>
+          <t>Em andamento</t>
         </is>
       </c>
       <c r="J135" s="0">
@@ -9398,20 +9398,20 @@
       </c>
       <c r="K135" s="0" t="inlineStr">
         <is>
+          <t>16/09/2026</t>
+        </is>
+      </c>
+      <c r="L135" s="0" t="inlineStr">
+        <is>
           <t>21/09/2026</t>
         </is>
       </c>
-      <c r="L135" s="0" t="inlineStr">
-        <is>
-          <t>21/09/2026</t>
-        </is>
-      </c>
       <c r="M135" s="3">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="N135" s="0" t="inlineStr">
         <is>
-          <t>Validadores cobrem caminhos felizes pulo limpeza de escolha reinício cancelamento de saída sugestão opcional persistência exportação e serviço integrado de produção — iniciar aceite formal após concluir 132 e 133 e confirmar troca entre jogos sem estado residual</t>
+          <t>API serviço integrado e matriz móvel revalidados com sucesso em 16/09/2026 após a passagem física no Chrome — pendem concluir as verificações formais de acessibilidade da tarefa 133 e registrar o aceite final — Safari permanece fora da cobertura atual</t>
         </is>
       </c>
     </row>
@@ -9477,7 +9477,7 @@
       </c>
       <c r="N136" s="0" t="inlineStr">
         <is>
-          <t>Demonstração HTTPS publicada no Render gratuito com Web Service PostgreSQL de 1 GB sonda de saúde CORS restrito bloqueio de indexação e segredo operacional — envio persistência e exportação validados base sintética removida e banco expira em 16/10/2026 sem backup — passagem física Android e iPhone continua na tarefa 132 antes de ampliar o teste</t>
+          <t>Demonstração HTTPS publicada no Render gratuito com Web Service PostgreSQL de 1 GB sonda de saúde CORS restrito bloqueio de indexação e segredo operacional — envio persistência exportação e passagem física no Chrome validados base técnica limpa e banco expira em 16/10/2026 sem backup — Safari permanece fora da cobertura atual</t>
         </is>
       </c>
     </row>
@@ -9851,7 +9851,7 @@
       </c>
       <c r="D3" s="0" t="inlineStr">
         <is>
-          <t>Não iniciado</t>
+          <t>Concluído</t>
         </is>
       </c>
       <c r="E3" s="0" t="inlineStr">
@@ -9886,12 +9886,12 @@
       </c>
       <c r="D4" s="0" t="inlineStr">
         <is>
-          <t>Não iniciado</t>
+          <t>Em andamento</t>
         </is>
       </c>
       <c r="E4" s="0" t="inlineStr">
         <is>
-          <t>QA crítico aprovado e link controlado disponível</t>
+          <t>Link controlado disponível e QA em curso com aceite físico restrito ao Chrome</t>
         </is>
       </c>
       <c r="F4" s="0" t="inlineStr">

--- a/Plano de trabalho/acompanhamento-app-do-amor.xlsx
+++ b/Plano de trabalho/acompanhamento-app-do-amor.xlsx
@@ -109,7 +109,7 @@
       </c>
       <c r="B2" s="0" t="inlineStr">
         <is>
-          <t>16/09/2026 21:11</t>
+          <t>17/09/2026 12:29</t>
         </is>
       </c>
       <c r="C2" s="0" t="inlineStr">
@@ -142,7 +142,7 @@
         </is>
       </c>
       <c r="B4" s="2">
-        <f>COUNTA('Plano Mestre'!A2:A140)</f>
+        <f>COUNTA('Plano Mestre'!A2:A143)</f>
         <v>0</v>
       </c>
       <c r="C4" s="0" t="inlineStr">
@@ -158,7 +158,7 @@
         </is>
       </c>
       <c r="B5" s="2">
-        <f>COUNTIF('Plano Mestre'!I2:I140,"Concluído")</f>
+        <f>COUNTIF('Plano Mestre'!I2:I143,"Concluído")</f>
         <v>0</v>
       </c>
       <c r="C5" s="0" t="inlineStr">
@@ -174,7 +174,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIF('Plano Mestre'!I2:I140,"Em andamento")</f>
+        <f>COUNTIF('Plano Mestre'!I2:I143,"Em andamento")</f>
         <v>0</v>
       </c>
       <c r="C6" s="0" t="inlineStr">
@@ -190,7 +190,7 @@
         </is>
       </c>
       <c r="B7" s="2">
-        <f>COUNTIF('Plano Mestre'!I2:I140,"Não iniciado")</f>
+        <f>COUNTIF('Plano Mestre'!I2:I143,"Não iniciado")</f>
         <v>0</v>
       </c>
       <c r="C7" s="0" t="inlineStr">
@@ -206,7 +206,7 @@
         </is>
       </c>
       <c r="B8" s="3">
-        <f>AVERAGE('Plano Mestre'!M2:M140)</f>
+        <f>AVERAGE('Plano Mestre'!M2:M143)</f>
         <v>0</v>
       </c>
       <c r="C8" s="0" t="inlineStr">
@@ -222,7 +222,7 @@
         </is>
       </c>
       <c r="B9" s="2">
-        <f>SUM('Plano Mestre'!J2:J140)</f>
+        <f>SUM('Plano Mestre'!J2:J143)</f>
         <v>0</v>
       </c>
       <c r="C9" s="0" t="inlineStr">
@@ -272,11 +272,11 @@
         </is>
       </c>
       <c r="B12" s="2">
-        <f>COUNTIF('Plano Mestre'!B2:B140,"Descoberta")</f>
+        <f>COUNTIF('Plano Mestre'!B2:B143,"Descoberta")</f>
         <v>0</v>
       </c>
       <c r="C12" s="2">
-        <f>COUNTIFS('Plano Mestre'!B2:B140,"Descoberta",'Plano Mestre'!I2:I140,"Concluído")</f>
+        <f>COUNTIFS('Plano Mestre'!B2:B143,"Descoberta",'Plano Mestre'!I2:I143,"Concluído")</f>
         <v>0</v>
       </c>
     </row>
@@ -287,11 +287,11 @@
         </is>
       </c>
       <c r="B13" s="2">
-        <f>COUNTIF('Plano Mestre'!B2:B140,"Planejamento")</f>
+        <f>COUNTIF('Plano Mestre'!B2:B143,"Planejamento")</f>
         <v>0</v>
       </c>
       <c r="C13" s="2">
-        <f>COUNTIFS('Plano Mestre'!B2:B140,"Planejamento",'Plano Mestre'!I2:I140,"Concluído")</f>
+        <f>COUNTIFS('Plano Mestre'!B2:B143,"Planejamento",'Plano Mestre'!I2:I143,"Concluído")</f>
         <v>0</v>
       </c>
     </row>
@@ -302,11 +302,11 @@
         </is>
       </c>
       <c r="B14" s="2">
-        <f>COUNTIF('Plano Mestre'!B2:B140,"Marca")</f>
+        <f>COUNTIF('Plano Mestre'!B2:B143,"Marca")</f>
         <v>0</v>
       </c>
       <c r="C14" s="2">
-        <f>COUNTIFS('Plano Mestre'!B2:B140,"Marca",'Plano Mestre'!I2:I140,"Concluído")</f>
+        <f>COUNTIFS('Plano Mestre'!B2:B143,"Marca",'Plano Mestre'!I2:I143,"Concluído")</f>
         <v>0</v>
       </c>
     </row>
@@ -317,11 +317,11 @@
         </is>
       </c>
       <c r="B15" s="2">
-        <f>COUNTIF('Plano Mestre'!B2:B140,"UX/UI")</f>
+        <f>COUNTIF('Plano Mestre'!B2:B143,"UX/UI")</f>
         <v>0</v>
       </c>
       <c r="C15" s="2">
-        <f>COUNTIFS('Plano Mestre'!B2:B140,"UX/UI",'Plano Mestre'!I2:I140,"Concluído")</f>
+        <f>COUNTIFS('Plano Mestre'!B2:B143,"UX/UI",'Plano Mestre'!I2:I143,"Concluído")</f>
         <v>0</v>
       </c>
     </row>
@@ -332,11 +332,11 @@
         </is>
       </c>
       <c r="B16" s="2">
-        <f>COUNTIF('Plano Mestre'!B2:B140,"Arquitetura")</f>
+        <f>COUNTIF('Plano Mestre'!B2:B143,"Arquitetura")</f>
         <v>0</v>
       </c>
       <c r="C16" s="2">
-        <f>COUNTIFS('Plano Mestre'!B2:B140,"Arquitetura",'Plano Mestre'!I2:I140,"Concluído")</f>
+        <f>COUNTIFS('Plano Mestre'!B2:B143,"Arquitetura",'Plano Mestre'!I2:I143,"Concluído")</f>
         <v>0</v>
       </c>
     </row>
@@ -347,11 +347,11 @@
         </is>
       </c>
       <c r="B17" s="2">
-        <f>COUNTIF('Plano Mestre'!B2:B140,"Infraestrutura")</f>
+        <f>COUNTIF('Plano Mestre'!B2:B143,"Infraestrutura")</f>
         <v>0</v>
       </c>
       <c r="C17" s="2">
-        <f>COUNTIFS('Plano Mestre'!B2:B140,"Infraestrutura",'Plano Mestre'!I2:I140,"Concluído")</f>
+        <f>COUNTIFS('Plano Mestre'!B2:B143,"Infraestrutura",'Plano Mestre'!I2:I143,"Concluído")</f>
         <v>0</v>
       </c>
     </row>
@@ -362,11 +362,11 @@
         </is>
       </c>
       <c r="B18" s="2">
-        <f>COUNTIF('Plano Mestre'!B2:B140,"Backend")</f>
+        <f>COUNTIF('Plano Mestre'!B2:B143,"Backend")</f>
         <v>0</v>
       </c>
       <c r="C18" s="2">
-        <f>COUNTIFS('Plano Mestre'!B2:B140,"Backend",'Plano Mestre'!I2:I140,"Concluído")</f>
+        <f>COUNTIFS('Plano Mestre'!B2:B143,"Backend",'Plano Mestre'!I2:I143,"Concluído")</f>
         <v>0</v>
       </c>
     </row>
@@ -377,11 +377,11 @@
         </is>
       </c>
       <c r="B19" s="2">
-        <f>COUNTIF('Plano Mestre'!B2:B140,"Frontend")</f>
+        <f>COUNTIF('Plano Mestre'!B2:B143,"Frontend")</f>
         <v>0</v>
       </c>
       <c r="C19" s="2">
-        <f>COUNTIFS('Plano Mestre'!B2:B140,"Frontend",'Plano Mestre'!I2:I140,"Concluído")</f>
+        <f>COUNTIFS('Plano Mestre'!B2:B143,"Frontend",'Plano Mestre'!I2:I143,"Concluído")</f>
         <v>0</v>
       </c>
     </row>
@@ -392,11 +392,11 @@
         </is>
       </c>
       <c r="B20" s="2">
-        <f>COUNTIF('Plano Mestre'!B2:B140,"Conteúdo")</f>
+        <f>COUNTIF('Plano Mestre'!B2:B143,"Conteúdo")</f>
         <v>0</v>
       </c>
       <c r="C20" s="2">
-        <f>COUNTIFS('Plano Mestre'!B2:B140,"Conteúdo",'Plano Mestre'!I2:I140,"Concluído")</f>
+        <f>COUNTIFS('Plano Mestre'!B2:B143,"Conteúdo",'Plano Mestre'!I2:I143,"Concluído")</f>
         <v>0</v>
       </c>
     </row>
@@ -407,11 +407,11 @@
         </is>
       </c>
       <c r="B21" s="2">
-        <f>COUNTIF('Plano Mestre'!B2:B140,"Qualidade")</f>
+        <f>COUNTIF('Plano Mestre'!B2:B143,"Qualidade")</f>
         <v>0</v>
       </c>
       <c r="C21" s="2">
-        <f>COUNTIFS('Plano Mestre'!B2:B140,"Qualidade",'Plano Mestre'!I2:I140,"Concluído")</f>
+        <f>COUNTIFS('Plano Mestre'!B2:B143,"Qualidade",'Plano Mestre'!I2:I143,"Concluído")</f>
         <v>0</v>
       </c>
     </row>
@@ -422,11 +422,11 @@
         </is>
       </c>
       <c r="B22" s="2">
-        <f>COUNTIF('Plano Mestre'!B2:B140,"Jurídico")</f>
+        <f>COUNTIF('Plano Mestre'!B2:B143,"Jurídico")</f>
         <v>0</v>
       </c>
       <c r="C22" s="2">
-        <f>COUNTIFS('Plano Mestre'!B2:B140,"Jurídico",'Plano Mestre'!I2:I140,"Concluído")</f>
+        <f>COUNTIFS('Plano Mestre'!B2:B143,"Jurídico",'Plano Mestre'!I2:I143,"Concluído")</f>
         <v>0</v>
       </c>
     </row>
@@ -437,11 +437,11 @@
         </is>
       </c>
       <c r="B23" s="2">
-        <f>COUNTIF('Plano Mestre'!B2:B140,"Lançamento")</f>
+        <f>COUNTIF('Plano Mestre'!B2:B143,"Lançamento")</f>
         <v>0</v>
       </c>
       <c r="C23" s="2">
-        <f>COUNTIFS('Plano Mestre'!B2:B140,"Lançamento",'Plano Mestre'!I2:I140,"Concluído")</f>
+        <f>COUNTIFS('Plano Mestre'!B2:B143,"Lançamento",'Plano Mestre'!I2:I143,"Concluído")</f>
         <v>0</v>
       </c>
     </row>
@@ -452,11 +452,11 @@
         </is>
       </c>
       <c r="B24" s="2">
-        <f>COUNTIF('Plano Mestre'!B2:B140,"Pós-lançamento")</f>
+        <f>COUNTIF('Plano Mestre'!B2:B143,"Pós-lançamento")</f>
         <v>0</v>
       </c>
       <c r="C24" s="2">
-        <f>COUNTIFS('Plano Mestre'!B2:B140,"Pós-lançamento",'Plano Mestre'!I2:I140,"Concluído")</f>
+        <f>COUNTIFS('Plano Mestre'!B2:B143,"Pós-lançamento",'Plano Mestre'!I2:I143,"Concluído")</f>
         <v>0</v>
       </c>
     </row>
@@ -467,11 +467,11 @@
         </is>
       </c>
       <c r="B25" s="2">
-        <f>COUNTIF('Plano Mestre'!B2:B140,"MPV de teste")</f>
+        <f>COUNTIF('Plano Mestre'!B2:B143,"MPV de teste")</f>
         <v>0</v>
       </c>
       <c r="C25" s="2">
-        <f>COUNTIFS('Plano Mestre'!B2:B140,"MPV de teste",'Plano Mestre'!I2:I140,"Concluído")</f>
+        <f>COUNTIFS('Plano Mestre'!B2:B143,"MPV de teste",'Plano Mestre'!I2:I143,"Concluído")</f>
         <v>0</v>
       </c>
     </row>
@@ -8817,7 +8817,7 @@
       </c>
       <c r="N126" s="0" t="inlineStr">
         <is>
-          <t>Somente Descoberta a Dois e Adivinhe de Mim — sem pesquisa prévia cadastro pareamento remoto backend ou testes de personalidade neste teste</t>
+          <t>Escopo inicial de Descoberta a Dois e Adivinhe de Mim concluído — exceção posterior autorizada pela Product Owner em 17/09/2026 adiciona amostra autoral e baralho visual nas tarefas 140 e 141</t>
         </is>
       </c>
     </row>
@@ -8875,7 +8875,7 @@
       </c>
       <c r="L127" s="0" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="M127" s="3">
@@ -8883,7 +8883,7 @@
       </c>
       <c r="N127" s="0" t="inlineStr">
         <is>
-          <t>Fluxo aprovado em docs/FLUXO-MPV.md com seis estados entrada direta dois jogos de três rodadas três sinais e sugestão opcional exceções e critérios de aceite — atualizado em 16/09/2026</t>
+          <t>Fluxo ampliado em docs/FLUXO-MPV.md com entrada direta três experiências cartas fechadas dois jogos amostra individual três sinais sugestão opcional exceções e critérios de aceite</t>
         </is>
       </c>
     </row>
@@ -9007,7 +9007,7 @@
       </c>
       <c r="L129" s="0" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="M129" s="3">
@@ -9015,7 +9015,7 @@
       </c>
       <c r="N129" s="0" t="inlineStr">
         <is>
-          <t>Entrada direta responsiva com seleção e instruções dos dois jogos implementada sem cadastro ou pareamento, com apresentação neutra sem o nome do aplicativo em título metadados cabeçalho ou rodapé e com o aplicativo completo preservado em src/App.tsx — atualizado em 14/09/2026</t>
+          <t>Entrada direta responsiva ampliada para três experiências sem cadastro ou pareamento com apresentação neutra sem o nome do aplicativo em título metadados cabeçalho ou rodapé e aplicativo completo preservado — atualizada em 17/09/2026</t>
         </is>
       </c>
     </row>
@@ -9205,7 +9205,7 @@
       </c>
       <c r="L132" s="0" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="M132" s="3">
@@ -9213,7 +9213,7 @@
       </c>
       <c r="N132" s="0" t="inlineStr">
         <is>
-          <t>Feedback binário compartilhado implementado nos dois jogos e integrado ao registro central do jogo concluído clareza descoberta ou conexão e intenção de jogar novamente sem conteúdo das rodadas — concluído antecipadamente em 12/09/2026 e integrado em 16/09/2026</t>
+          <t>Feedback binário integrado aos dois jogos e à amostra individual com textos adaptados e registro central de clareza reflexão ou conexão e intenção de repetir sem respostas das rodadas — ampliado em 17/09/2026</t>
         </is>
       </c>
     </row>
@@ -9345,7 +9345,7 @@
       </c>
       <c r="N134" s="0" t="inlineStr">
         <is>
-          <t>MOB-03 resolvido em 14/09/2026 com todos os alvos visíveis em pelo menos 44 px e nomes acessíveis aprovados na matriz móvel — pendentes validações formais de foco contraste e redução de movimento</t>
+          <t>Todos os alvos incluindo cartas fechadas permanecem com pelo menos 44 px e nomes acessíveis aprovados em 185 estados móveis — pendentes validações formais de foco contraste e redução de movimento</t>
         </is>
       </c>
     </row>
@@ -9411,7 +9411,7 @@
       </c>
       <c r="N135" s="0" t="inlineStr">
         <is>
-          <t>API serviço integrado e matriz móvel revalidados com sucesso em 16/09/2026 após a passagem física no Chrome — pendem concluir as verificações formais de acessibilidade da tarefa 133 e registrar o aceite final — Safari permanece fora da cobertura atual</t>
+          <t>API serviço integrado três experiências baralho visual e matriz de 185 estados revalidados automaticamente em 17/09/2026 — pendem verificações formais da tarefa 133 e nova passagem física da tarefa 142 — Safari fora da cobertura atual</t>
         </is>
       </c>
     </row>
@@ -9512,7 +9512,7 @@
       </c>
       <c r="G137" s="0" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>135,142</t>
         </is>
       </c>
       <c r="H137" s="0" t="inlineStr">
@@ -9543,7 +9543,7 @@
       </c>
       <c r="N137" s="0" t="inlineStr">
         <is>
-          <t>Cada casal joga sem mediação e envia os três sinais do produto com sugestão de melhoria opcional — não há entrevistas nem etapa de pesquisa dentro do MPV</t>
+          <t>Cada casal usa as experiências sem mediação e envia os três sinais do produto com sugestão de melhoria opcional — não há entrevistas nem etapa de pesquisa dentro do MPV — iniciar após a nova passagem física da versão ampliada</t>
         </is>
       </c>
     </row>
@@ -9745,8 +9745,206 @@
         </is>
       </c>
     </row>
+    <row r="141">
+      <c r="A141" s="0">
+        <v>140</v>
+      </c>
+      <c r="B141" s="0" t="inlineStr">
+        <is>
+          <t>MPV de teste</t>
+        </is>
+      </c>
+      <c r="C141" s="0" t="inlineStr">
+        <is>
+          <t>Experimento</t>
+        </is>
+      </c>
+      <c r="D141" s="0" t="inlineStr">
+        <is>
+          <t>Adicionar amostra autoral de preferências afetivas</t>
+        </is>
+      </c>
+      <c r="E141" s="0" t="inlineStr">
+        <is>
+          <t>Amostra individual funcional</t>
+        </is>
+      </c>
+      <c r="F141" s="0" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="G141" s="0" t="inlineStr">
+        <is>
+          <t>126,128,139</t>
+        </is>
+      </c>
+      <c r="H141" s="0" t="inlineStr">
+        <is>
+          <t>Engenharia Frontend</t>
+        </is>
+      </c>
+      <c r="I141" s="0" t="inlineStr">
+        <is>
+          <t>Concluído</t>
+        </is>
+      </c>
+      <c r="J141" s="0">
+        <v>10</v>
+      </c>
+      <c r="K141" s="0" t="inlineStr">
+        <is>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="L141" s="0" t="inlineStr">
+        <is>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="M141" s="3">
+        <v>1</v>
+      </c>
+      <c r="N141" s="0" t="inlineStr">
+        <is>
+          <t>Cinco perguntas sorteadas entre seis situações autorais com cinco famílias de preferência pontuação somente em memória resultado com duas preferências fortes distribuição completa aviso não oficial e feedback adaptado — conteúdo não replica questionários comerciais</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="0">
+        <v>141</v>
+      </c>
+      <c r="B142" s="0" t="inlineStr">
+        <is>
+          <t>MPV de teste</t>
+        </is>
+      </c>
+      <c r="C142" s="0" t="inlineStr">
+        <is>
+          <t>UX</t>
+        </is>
+      </c>
+      <c r="D142" s="0" t="inlineStr">
+        <is>
+          <t>Apresentar perguntas como cartas fechadas escolhidas pela pessoa</t>
+        </is>
+      </c>
+      <c r="E142" s="0" t="inlineStr">
+        <is>
+          <t>Baralho visual acessível</t>
+        </is>
+      </c>
+      <c r="F142" s="0" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="G142" s="0" t="inlineStr">
+        <is>
+          <t>129,130,140</t>
+        </is>
+      </c>
+      <c r="H142" s="0" t="inlineStr">
+        <is>
+          <t>Engenharia Frontend</t>
+        </is>
+      </c>
+      <c r="I142" s="0" t="inlineStr">
+        <is>
+          <t>Concluído</t>
+        </is>
+      </c>
+      <c r="J142" s="0">
+        <v>8</v>
+      </c>
+      <c r="K142" s="0" t="inlineStr">
+        <is>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="L142" s="0" t="inlineStr">
+        <is>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="M142" s="3">
+        <v>1</v>
+      </c>
+      <c r="N142" s="0" t="inlineStr">
+        <is>
+          <t>Componente visual em HTML e CSS aplicado às três experiências com escolha real entre cartas restantes animação rótulos acessíveis alvos mínimos de 44 px redução de movimento e reinício validado</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="0">
+        <v>142</v>
+      </c>
+      <c r="B143" s="0" t="inlineStr">
+        <is>
+          <t>MPV de teste</t>
+        </is>
+      </c>
+      <c r="C143" s="0" t="inlineStr">
+        <is>
+          <t>Qualidade</t>
+        </is>
+      </c>
+      <c r="D143" s="0" t="inlineStr">
+        <is>
+          <t>Revalidar versão ampliada e repetir passagem física no Chrome</t>
+        </is>
+      </c>
+      <c r="E143" s="0" t="inlineStr">
+        <is>
+          <t>Aceite da iteração ampliada</t>
+        </is>
+      </c>
+      <c r="F143" s="0" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+      <c r="G143" s="0" t="inlineStr">
+        <is>
+          <t>133,134,140,141</t>
+        </is>
+      </c>
+      <c r="H143" s="0" t="inlineStr">
+        <is>
+          <t>Qualidade</t>
+        </is>
+      </c>
+      <c r="I143" s="0" t="inlineStr">
+        <is>
+          <t>Em andamento</t>
+        </is>
+      </c>
+      <c r="J143" s="0">
+        <v>4</v>
+      </c>
+      <c r="K143" s="0" t="inlineStr">
+        <is>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="L143" s="0" t="inlineStr">
+        <is>
+          <t>18/09/2026</t>
+        </is>
+      </c>
+      <c r="M143" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="N143" s="0" t="inlineStr">
+        <is>
+          <t>Matriz emulada aprovada com cinco viewports 185 estados 15 feedbacks sintéticos três experiências baralho resultado e ausência do nome do aplicativo — pendente publicar validar PostgreSQL e repetir passagem física no Chrome — Safari segue adiado</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N140"/>
+  <autoFilter ref="A1:N143"/>
   <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
 </worksheet>
 </file>
@@ -9843,11 +10041,11 @@
       </c>
       <c r="B3" s="0" t="inlineStr">
         <is>
-          <t>Dois jogos jogáveis</t>
+          <t>Três experiências jogáveis</t>
         </is>
       </c>
       <c r="C3" s="0">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="D3" s="0" t="inlineStr">
         <is>
@@ -9856,12 +10054,12 @@
       </c>
       <c r="E3" s="0" t="inlineStr">
         <is>
-          <t>Jornadas completas com lote mínimo e feedback no produto</t>
+          <t>Dois jogos amostra autoral baralho visual e feedback funcionando</t>
         </is>
       </c>
       <c r="F3" s="0" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="G3" s="0" t="inlineStr">
@@ -9882,7 +10080,7 @@
         </is>
       </c>
       <c r="C4" s="0">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="D4" s="0" t="inlineStr">
         <is>
@@ -9891,7 +10089,7 @@
       </c>
       <c r="E4" s="0" t="inlineStr">
         <is>
-          <t>Link controlado disponível e QA em curso com aceite físico restrito ao Chrome</t>
+          <t>Link controlado disponível e nova passagem física da versão ampliada pendente no Chrome</t>
         </is>
       </c>
       <c r="F4" s="0" t="inlineStr">
@@ -10463,7 +10661,7 @@
       </c>
       <c r="F4" s="0" t="inlineStr">
         <is>
-          <t>Revisão por especialista e avisos claros de caráter educativo</t>
+          <t>Amostra autoral com aviso não oficial e não diagnóstico — manter revisão especializada antes de ampliar</t>
         </is>
       </c>
       <c r="G4" s="0" t="inlineStr">
@@ -10967,7 +11165,7 @@
       </c>
       <c r="F16" s="0" t="inlineStr">
         <is>
-          <t>Bloquear novas áreas no teste e exigir a retirada de um item para qualquer inclusão</t>
+          <t>Ampliação autorizada pela Product Owner em 17/09/2026 — separar sinais por experiência e exigir revalidação física antes dos cinco casais</t>
         </is>
       </c>
       <c r="G16" s="0" t="inlineStr">
@@ -10977,7 +11175,7 @@
       </c>
       <c r="H16" s="0" t="inlineStr">
         <is>
-          <t>Aberto</t>
+          <t>Em acompanhamento</t>
         </is>
       </c>
     </row>
@@ -11093,7 +11291,7 @@
       </c>
       <c r="F19" s="0" t="inlineStr">
         <is>
-          <t>Equilibrar duração tema e quantidade de cartas entre os dois jogos</t>
+          <t>Analisar feedback separadamente entre os dois jogos e a amostra autoral para não misturar efeito de conteúdo e interação</t>
         </is>
       </c>
       <c r="G19" s="0" t="inlineStr">

--- a/Plano de trabalho/acompanhamento-app-do-amor.xlsx
+++ b/Plano de trabalho/acompanhamento-app-do-amor.xlsx
@@ -109,7 +109,7 @@
       </c>
       <c r="B2" s="0" t="inlineStr">
         <is>
-          <t>17/09/2026 12:29</t>
+          <t>17/09/2026 12:33</t>
         </is>
       </c>
       <c r="C2" s="0" t="inlineStr">
@@ -9469,7 +9469,7 @@
       </c>
       <c r="L136" s="0" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="M136" s="3">
@@ -9477,7 +9477,7 @@
       </c>
       <c r="N136" s="0" t="inlineStr">
         <is>
-          <t>Demonstração HTTPS publicada no Render gratuito com Web Service PostgreSQL de 1 GB sonda de saúde CORS restrito bloqueio de indexação e segredo operacional — envio persistência exportação e passagem física no Chrome validados base técnica limpa e banco expira em 16/10/2026 sem backup — Safari permanece fora da cobertura atual</t>
+          <t>Versão ampliada publicada por HTTPS no Render gratuito com três experiências baralho visual Web Service PostgreSQL de 1 GB sonda de saúde CORS restrito bloqueio de indexação e segredo operacional — novo gameId persistido e exportado base técnica limpa e banco expira em 16/10/2026 sem backup</t>
         </is>
       </c>
     </row>
@@ -9733,7 +9733,7 @@
       </c>
       <c r="L140" s="0" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="M140" s="3">
@@ -9741,7 +9741,7 @@
       </c>
       <c r="N140" s="0" t="inlineStr">
         <is>
-          <t>POST anônimo com validação idempotência controle de origem rate limit armazenamento PostgreSQL remoto com fallback JSON local e exportação CSV protegida por token — concluído em 16/09/2026</t>
+          <t>POST anônimo com validação idempotência controle de origem rate limit armazenamento PostgreSQL remoto fallback JSON local e exportação CSV protegida — schema ampliado e validado ao vivo para love-style-sample em 17/09/2026 sem armazenar respostas ou resultado</t>
         </is>
       </c>
     </row>
@@ -9939,7 +9939,7 @@
       </c>
       <c r="N143" s="0" t="inlineStr">
         <is>
-          <t>Matriz emulada aprovada com cinco viewports 185 estados 15 feedbacks sintéticos três experiências baralho resultado e ausência do nome do aplicativo — pendente publicar validar PostgreSQL e repetir passagem física no Chrome — Safari segue adiado</t>
+          <t>Versão ampliada publicada e aprovada em cinco viewports 185 estados 15 feedbacks sintéticos três experiências baralho resultado nome oculto PostgreSQL e exportação ao vivo — registro técnico removido e acesso externo ao banco fechado — pendente somente repetir a passagem física no Chrome — Safari segue adiado</t>
         </is>
       </c>
     </row>

--- a/Plano de trabalho/acompanhamento-app-do-amor.xlsx
+++ b/Plano de trabalho/acompanhamento-app-do-amor.xlsx
@@ -109,7 +109,7 @@
       </c>
       <c r="B2" s="0" t="inlineStr">
         <is>
-          <t>17/09/2026 12:33</t>
+          <t>17/09/2026 16:44</t>
         </is>
       </c>
       <c r="C2" s="0" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="I41" s="0" t="inlineStr">
         <is>
-          <t>Não iniciado</t>
+          <t>Em andamento</t>
         </is>
       </c>
       <c r="J41" s="0">
@@ -3194,7 +3194,7 @@
       </c>
       <c r="K41" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="L41" s="0" t="inlineStr">
@@ -3203,11 +3203,11 @@
         </is>
       </c>
       <c r="M41" s="3">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="N41" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>Workflow GitHub Actions criado em .github/workflows/ci.yml com Ubuntu 24.04 Node 24.20.0 cache npm instalação por lockfile permissões somente leitura concorrência timeout e gates de lint formato build OpenAPI ameaças LGPD feedback produção matriz móvel e planilha — documentação em docs/INTEGRACAO-CONTINUA.md — aguarda primeira execução remota aprovada</t>
         </is>
       </c>
     </row>

--- a/Plano de trabalho/acompanhamento-app-do-amor.xlsx
+++ b/Plano de trabalho/acompanhamento-app-do-amor.xlsx
@@ -109,7 +109,7 @@
       </c>
       <c r="B2" s="0" t="inlineStr">
         <is>
-          <t>17/09/2026 16:44</t>
+          <t>17/09/2026 16:55</t>
         </is>
       </c>
       <c r="C2" s="0" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="I41" s="0" t="inlineStr">
         <is>
-          <t>Em andamento</t>
+          <t>Concluído</t>
         </is>
       </c>
       <c r="J41" s="0">
@@ -3199,15 +3199,15 @@
       </c>
       <c r="L41" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="M41" s="3">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="N41" s="0" t="inlineStr">
         <is>
-          <t>Workflow GitHub Actions criado em .github/workflows/ci.yml com Ubuntu 24.04 Node 24.20.0 cache npm instalação por lockfile permissões somente leitura concorrência timeout e gates de lint formato build OpenAPI ameaças LGPD feedback produção matriz móvel e planilha — documentação em docs/INTEGRACAO-CONTINUA.md — aguarda primeira execução remota aprovada</t>
+          <t>Workflow GitHub Actions em .github/workflows/ci.yml com Ubuntu 24.04 Node 24.20.0 cache npm instalação por lockfile permissões somente leitura concorrência timeout e gates de lint formato build OpenAPI ameaças LGPD feedback produção matriz móvel e planilha — documentação em docs/INTEGRACAO-CONTINUA.md — execução remota 1 aprovada em https://github.com/tatyelopes/APPDOAMOR/actions/runs/35267092012</t>
         </is>
       </c>
     </row>

--- a/Plano de trabalho/acompanhamento-app-do-amor.xlsx
+++ b/Plano de trabalho/acompanhamento-app-do-amor.xlsx
@@ -109,7 +109,7 @@
       </c>
       <c r="B2" s="0" t="inlineStr">
         <is>
-          <t>17/09/2026 16:55</t>
+          <t>17/09/2026 17:12</t>
         </is>
       </c>
       <c r="C2" s="0" t="inlineStr">
@@ -3260,7 +3260,7 @@
       </c>
       <c r="K42" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L42" s="0" t="inlineStr">
@@ -3273,7 +3273,7 @@
       </c>
       <c r="N42" s="0" t="inlineStr">
         <is>
-          <t>Adaptador DATABASE_URL e schema idempotente implementados para o feedback do MPV em 16/09/2026 com PostgreSQL gratuito temporário no Render - ainda provisionar local staging e production definitivos com identidades distintas migrações integridade concorrência e migração dos demais dados</t>
+          <t>PostgreSQL gratuito temporário do feedback ativo no Render — em 17/09/2026 foram adicionados PostgreSQL 18 local via Compose executor transacional com lock e checksum duas migrações versionadas para 12 tabelas de domínio mais schema_migrations e validação real no CI — ainda integrar cadastro casal sessões respostas e analytics migrar dados legados com reconciliação e provisionar homologação e produção definitivas isoladas</t>
         </is>
       </c>
     </row>

--- a/Plano de trabalho/acompanhamento-app-do-amor.xlsx
+++ b/Plano de trabalho/acompanhamento-app-do-amor.xlsx
@@ -109,7 +109,7 @@
       </c>
       <c r="B2" s="0" t="inlineStr">
         <is>
-          <t>17/09/2026 17:12</t>
+          <t>17/09/2026 17:19</t>
         </is>
       </c>
       <c r="C2" s="0" t="inlineStr">
@@ -3273,7 +3273,7 @@
       </c>
       <c r="N42" s="0" t="inlineStr">
         <is>
-          <t>PostgreSQL gratuito temporário do feedback ativo no Render — em 17/09/2026 foram adicionados PostgreSQL 18 local via Compose executor transacional com lock e checksum duas migrações versionadas para 12 tabelas de domínio mais schema_migrations e validação real no CI — ainda integrar cadastro casal sessões respostas e analytics migrar dados legados com reconciliação e provisionar homologação e produção definitivas isoladas</t>
+          <t>PostgreSQL gratuito temporário do feedback ativo no Render — em 17/09/2026 foram adicionados PostgreSQL 18 local via Compose executor transacional com lock e checksum duas migrações versionadas para 12 tabelas de domínio mais schema_migrations e validação real aprovada em https://github.com/tatyelopes/APPDOAMOR/actions/runs/35269876662 — ainda integrar cadastro casal sessões respostas e analytics migrar dados legados com reconciliação e provisionar homologação e produção definitivas isoladas</t>
         </is>
       </c>
     </row>

--- a/Plano de trabalho/acompanhamento-app-do-amor.xlsx
+++ b/Plano de trabalho/acompanhamento-app-do-amor.xlsx
@@ -109,7 +109,7 @@
       </c>
       <c r="B2" s="0" t="inlineStr">
         <is>
-          <t>17/09/2026 17:19</t>
+          <t>17/09/2026 17:39</t>
         </is>
       </c>
       <c r="C2" s="0" t="inlineStr">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="I43" s="0" t="inlineStr">
         <is>
-          <t>Não iniciado</t>
+          <t>Em andamento</t>
         </is>
       </c>
       <c r="J43" s="0">
@@ -3326,7 +3326,7 @@
       </c>
       <c r="K43" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="L43" s="0" t="inlineStr">
@@ -3335,11 +3335,11 @@
         </is>
       </c>
       <c r="M43" s="3">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="N43" s="0" t="inlineStr">
         <is>
-          <t>Cofre identidades e chaves exclusivos por ambiente conforme docs/AMBIENTES.md - injeção em runtime privilégio mínimo inventário rotação e auditoria - modelos e gitignore não substituem esses controles</t>
+          <t>Baseline gratuita implementada em docs/GESTAO-DE-SEGREDOS.md com inventário matriz por ambiente geração local criptograficamente aleatória sem exibição validação fail-closed em runtime scanner de arquivos rastreados e staged hook pre-commit gate no CI modelo de rotação e injeção atual do Render — pendentes cofres e identidades definitivos de homologação e produção responsáveis nominais e primeira rotação comprovada</t>
         </is>
       </c>
     </row>

--- a/Plano de trabalho/acompanhamento-app-do-amor.xlsx
+++ b/Plano de trabalho/acompanhamento-app-do-amor.xlsx
@@ -109,7 +109,7 @@
       </c>
       <c r="B2" s="0" t="inlineStr">
         <is>
-          <t>17/09/2026 17:39</t>
+          <t>17/09/2026 17:44</t>
         </is>
       </c>
       <c r="C2" s="0" t="inlineStr">
@@ -3339,7 +3339,7 @@
       </c>
       <c r="N43" s="0" t="inlineStr">
         <is>
-          <t>Baseline gratuita implementada em docs/GESTAO-DE-SEGREDOS.md com inventário matriz por ambiente geração local criptograficamente aleatória sem exibição validação fail-closed em runtime scanner de arquivos rastreados e staged hook pre-commit gate no CI modelo de rotação e injeção atual do Render — pendentes cofres e identidades definitivos de homologação e produção responsáveis nominais e primeira rotação comprovada</t>
+          <t>Baseline gratuita implementada em docs/GESTAO-DE-SEGREDOS.md com inventário matriz por ambiente geração local criptograficamente aleatória sem exibição validação fail-closed em runtime scanner de arquivos rastreados staged e histórico hook pre-commit gate aprovado em https://github.com/tatyelopes/APPDOAMOR/actions/runs/35272382976 modelo de rotação e injeção atual do Render — pendentes cofres e identidades definitivos de homologação e produção responsáveis nominais e primeira rotação comprovada</t>
         </is>
       </c>
     </row>

--- a/Plano de trabalho/acompanhamento-app-do-amor.xlsx
+++ b/Plano de trabalho/acompanhamento-app-do-amor.xlsx
@@ -109,7 +109,7 @@
       </c>
       <c r="B2" s="0" t="inlineStr">
         <is>
-          <t>17/09/2026 17:44</t>
+          <t>17/09/2026 20:43</t>
         </is>
       </c>
       <c r="C2" s="0" t="inlineStr">
@@ -3273,7 +3273,7 @@
       </c>
       <c r="N42" s="0" t="inlineStr">
         <is>
-          <t>PostgreSQL gratuito temporário do feedback ativo no Render — em 17/09/2026 foram adicionados PostgreSQL 18 local via Compose executor transacional com lock e checksum duas migrações versionadas para 12 tabelas de domínio mais schema_migrations e validação real aprovada em https://github.com/tatyelopes/APPDOAMOR/actions/runs/35269876662 — ainda integrar cadastro casal sessões respostas e analytics migrar dados legados com reconciliação e provisionar homologação e produção definitivas isoladas</t>
+          <t>PostgreSQL gratuito temporário do feedback ativo no Render — em 17/09/2026 foram adicionados PostgreSQL 18 local via Compose executor transacional com lock e checksum duas migrações versionadas para 12 tabelas de domínio mais schema_migrations validação real aprovada em https://github.com/tatyelopes/APPDOAMOR/actions/runs/35269876662 e bootstrap automático da API para aplicar migrações antes de aceitar tráfego — ainda integrar cadastro casal sessões respostas e analytics migrar dados legados com reconciliação e provisionar homologação e produção definitivas isoladas</t>
         </is>
       </c>
     </row>
@@ -3339,7 +3339,7 @@
       </c>
       <c r="N43" s="0" t="inlineStr">
         <is>
-          <t>Baseline gratuita implementada em docs/GESTAO-DE-SEGREDOS.md com inventário matriz por ambiente geração local criptograficamente aleatória sem exibição validação fail-closed em runtime scanner de arquivos rastreados staged e histórico hook pre-commit gate aprovado em https://github.com/tatyelopes/APPDOAMOR/actions/runs/35272382976 modelo de rotação e injeção atual do Render — pendentes cofres e identidades definitivos de homologação e produção responsáveis nominais e primeira rotação comprovada</t>
+          <t>Baseline gratuita implementada em docs/GESTAO-DE-SEGREDOS.md com inventário matriz por ambiente geração local criptograficamente aleatória sem exibição validação fail-closed em runtime scanner de arquivos rastreados staged e histórico hook pre-commit gate aprovado em https://github.com/tatyelopes/APPDOAMOR/actions/runs/35272382976 modelo de rotação e injeção atual do Render — token de exportação do MPV rotacionado em 17/09/2026 após exposição acidental e salvo localmente sem exibição — pendentes cofres e identidades definitivos de homologação e produção e responsáveis nominais</t>
         </is>
       </c>
     </row>

--- a/Plano de trabalho/acompanhamento-app-do-amor.xlsx
+++ b/Plano de trabalho/acompanhamento-app-do-amor.xlsx
@@ -109,7 +109,7 @@
       </c>
       <c r="B2" s="0" t="inlineStr">
         <is>
-          <t>17/09/2026 20:43</t>
+          <t>17/09/2026 20:50</t>
         </is>
       </c>
       <c r="C2" s="0" t="inlineStr">
@@ -3273,7 +3273,7 @@
       </c>
       <c r="N42" s="0" t="inlineStr">
         <is>
-          <t>PostgreSQL gratuito temporário do feedback ativo no Render — em 17/09/2026 foram adicionados PostgreSQL 18 local via Compose executor transacional com lock e checksum duas migrações versionadas para 12 tabelas de domínio mais schema_migrations validação real aprovada em https://github.com/tatyelopes/APPDOAMOR/actions/runs/35269876662 e bootstrap automático da API para aplicar migrações antes de aceitar tráfego — ainda integrar cadastro casal sessões respostas e analytics migrar dados legados com reconciliação e provisionar homologação e produção definitivas isoladas</t>
+          <t>PostgreSQL gratuito temporário do feedback ativo no Render — em 17/09/2026 foram adicionados PostgreSQL 18 local via Compose executor transacional com lock e checksum duas migrações versionadas para 12 tabelas de domínio mais schema_migrations validação real aprovada em https://github.com/tatyelopes/APPDOAMOR/actions/runs/35269876662 e bootstrap automático da API aprovado no CI em https://github.com/tatyelopes/APPDOAMOR/actions/runs/35288177777 — após novo deploy a migração automática e a exportação protegida foram confirmadas ao vivo com base vazia — ainda integrar cadastro casal sessões respostas e analytics migrar dados legados com reconciliação e provisionar homologação e produção definitivas isoladas</t>
         </is>
       </c>
     </row>

--- a/Plano de trabalho/acompanhamento-app-do-amor.xlsx
+++ b/Plano de trabalho/acompanhamento-app-do-amor.xlsx
@@ -109,7 +109,7 @@
       </c>
       <c r="B2" s="0" t="inlineStr">
         <is>
-          <t>17/09/2026 20:50</t>
+          <t>17/09/2026 21:09</t>
         </is>
       </c>
       <c r="C2" s="0" t="inlineStr">
@@ -3384,7 +3384,7 @@
       </c>
       <c r="I44" s="0" t="inlineStr">
         <is>
-          <t>Em andamento</t>
+          <t>Concluído</t>
         </is>
       </c>
       <c r="J44" s="0">
@@ -3392,20 +3392,20 @@
       </c>
       <c r="K44" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="L44" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="M44" s="3">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="N44" s="0" t="inlineStr">
         <is>
-          <t>Sonda mínima GET /api/health implementada sem dados privados em 16/09/2026 - ainda separar logs métricas e alertas por ambiente e versão implementar prontidão do armazenamento e testar alertas de indisponibilidade erros banco backup e capacidade sem conteúdo íntimo ou segredos</t>
+          <t>Logs JSON com ambiente versão request ID rota normalizada status e duração sem corpo ou mensagem interna — erros 500 genéricos — sondas separadas de vida e prontidão com consulta real ao PostgreSQL — métricas de requisições erros prontidão latência memória e uptime protegidas — monitor gratuito do GitHub a cada 15 minutos com três tentativas abertura de issue única e encerramento após recuperação — teste com canário privado e documentação em docs/OBSERVABILIDADE.md — histórico durável thresholds por ambiente e alertas de backup seguem nas tarefas 123 118 e 93</t>
         </is>
       </c>
     </row>

--- a/Plano de trabalho/acompanhamento-app-do-amor.xlsx
+++ b/Plano de trabalho/acompanhamento-app-do-amor.xlsx
@@ -109,7 +109,7 @@
       </c>
       <c r="B2" s="0" t="inlineStr">
         <is>
-          <t>17/09/2026 21:09</t>
+          <t>23/09/2026 22:38</t>
         </is>
       </c>
       <c r="C2" s="0" t="inlineStr">
@@ -142,7 +142,7 @@
         </is>
       </c>
       <c r="B4" s="2">
-        <f>COUNTA('Plano Mestre'!A2:A143)</f>
+        <f>COUNTA('Plano Mestre'!A2:A145)</f>
         <v>0</v>
       </c>
       <c r="C4" s="0" t="inlineStr">
@@ -158,7 +158,7 @@
         </is>
       </c>
       <c r="B5" s="2">
-        <f>COUNTIF('Plano Mestre'!I2:I143,"Concluído")</f>
+        <f>COUNTIF('Plano Mestre'!I2:I145,"Concluído")</f>
         <v>0</v>
       </c>
       <c r="C5" s="0" t="inlineStr">
@@ -174,7 +174,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIF('Plano Mestre'!I2:I143,"Em andamento")</f>
+        <f>COUNTIF('Plano Mestre'!I2:I145,"Em andamento")</f>
         <v>0</v>
       </c>
       <c r="C6" s="0" t="inlineStr">
@@ -190,7 +190,7 @@
         </is>
       </c>
       <c r="B7" s="2">
-        <f>COUNTIF('Plano Mestre'!I2:I143,"Não iniciado")</f>
+        <f>COUNTIF('Plano Mestre'!I2:I145,"Não iniciado")</f>
         <v>0</v>
       </c>
       <c r="C7" s="0" t="inlineStr">
@@ -206,7 +206,7 @@
         </is>
       </c>
       <c r="B8" s="3">
-        <f>AVERAGE('Plano Mestre'!M2:M143)</f>
+        <f>AVERAGE('Plano Mestre'!M2:M145)</f>
         <v>0</v>
       </c>
       <c r="C8" s="0" t="inlineStr">
@@ -222,7 +222,7 @@
         </is>
       </c>
       <c r="B9" s="2">
-        <f>SUM('Plano Mestre'!J2:J143)</f>
+        <f>SUM('Plano Mestre'!J2:J145)</f>
         <v>0</v>
       </c>
       <c r="C9" s="0" t="inlineStr">
@@ -272,11 +272,11 @@
         </is>
       </c>
       <c r="B12" s="2">
-        <f>COUNTIF('Plano Mestre'!B2:B143,"Descoberta")</f>
+        <f>COUNTIF('Plano Mestre'!B2:B145,"Descoberta")</f>
         <v>0</v>
       </c>
       <c r="C12" s="2">
-        <f>COUNTIFS('Plano Mestre'!B2:B143,"Descoberta",'Plano Mestre'!I2:I143,"Concluído")</f>
+        <f>COUNTIFS('Plano Mestre'!B2:B145,"Descoberta",'Plano Mestre'!I2:I145,"Concluído")</f>
         <v>0</v>
       </c>
     </row>
@@ -287,11 +287,11 @@
         </is>
       </c>
       <c r="B13" s="2">
-        <f>COUNTIF('Plano Mestre'!B2:B143,"Planejamento")</f>
+        <f>COUNTIF('Plano Mestre'!B2:B145,"Planejamento")</f>
         <v>0</v>
       </c>
       <c r="C13" s="2">
-        <f>COUNTIFS('Plano Mestre'!B2:B143,"Planejamento",'Plano Mestre'!I2:I143,"Concluído")</f>
+        <f>COUNTIFS('Plano Mestre'!B2:B145,"Planejamento",'Plano Mestre'!I2:I145,"Concluído")</f>
         <v>0</v>
       </c>
     </row>
@@ -302,11 +302,11 @@
         </is>
       </c>
       <c r="B14" s="2">
-        <f>COUNTIF('Plano Mestre'!B2:B143,"Marca")</f>
+        <f>COUNTIF('Plano Mestre'!B2:B145,"Marca")</f>
         <v>0</v>
       </c>
       <c r="C14" s="2">
-        <f>COUNTIFS('Plano Mestre'!B2:B143,"Marca",'Plano Mestre'!I2:I143,"Concluído")</f>
+        <f>COUNTIFS('Plano Mestre'!B2:B145,"Marca",'Plano Mestre'!I2:I145,"Concluído")</f>
         <v>0</v>
       </c>
     </row>
@@ -317,11 +317,11 @@
         </is>
       </c>
       <c r="B15" s="2">
-        <f>COUNTIF('Plano Mestre'!B2:B143,"UX/UI")</f>
+        <f>COUNTIF('Plano Mestre'!B2:B145,"UX/UI")</f>
         <v>0</v>
       </c>
       <c r="C15" s="2">
-        <f>COUNTIFS('Plano Mestre'!B2:B143,"UX/UI",'Plano Mestre'!I2:I143,"Concluído")</f>
+        <f>COUNTIFS('Plano Mestre'!B2:B145,"UX/UI",'Plano Mestre'!I2:I145,"Concluído")</f>
         <v>0</v>
       </c>
     </row>
@@ -332,11 +332,11 @@
         </is>
       </c>
       <c r="B16" s="2">
-        <f>COUNTIF('Plano Mestre'!B2:B143,"Arquitetura")</f>
+        <f>COUNTIF('Plano Mestre'!B2:B145,"Arquitetura")</f>
         <v>0</v>
       </c>
       <c r="C16" s="2">
-        <f>COUNTIFS('Plano Mestre'!B2:B143,"Arquitetura",'Plano Mestre'!I2:I143,"Concluído")</f>
+        <f>COUNTIFS('Plano Mestre'!B2:B145,"Arquitetura",'Plano Mestre'!I2:I145,"Concluído")</f>
         <v>0</v>
       </c>
     </row>
@@ -347,11 +347,11 @@
         </is>
       </c>
       <c r="B17" s="2">
-        <f>COUNTIF('Plano Mestre'!B2:B143,"Infraestrutura")</f>
+        <f>COUNTIF('Plano Mestre'!B2:B145,"Infraestrutura")</f>
         <v>0</v>
       </c>
       <c r="C17" s="2">
-        <f>COUNTIFS('Plano Mestre'!B2:B143,"Infraestrutura",'Plano Mestre'!I2:I143,"Concluído")</f>
+        <f>COUNTIFS('Plano Mestre'!B2:B145,"Infraestrutura",'Plano Mestre'!I2:I145,"Concluído")</f>
         <v>0</v>
       </c>
     </row>
@@ -362,11 +362,11 @@
         </is>
       </c>
       <c r="B18" s="2">
-        <f>COUNTIF('Plano Mestre'!B2:B143,"Backend")</f>
+        <f>COUNTIF('Plano Mestre'!B2:B145,"Backend")</f>
         <v>0</v>
       </c>
       <c r="C18" s="2">
-        <f>COUNTIFS('Plano Mestre'!B2:B143,"Backend",'Plano Mestre'!I2:I143,"Concluído")</f>
+        <f>COUNTIFS('Plano Mestre'!B2:B145,"Backend",'Plano Mestre'!I2:I145,"Concluído")</f>
         <v>0</v>
       </c>
     </row>
@@ -377,11 +377,11 @@
         </is>
       </c>
       <c r="B19" s="2">
-        <f>COUNTIF('Plano Mestre'!B2:B143,"Frontend")</f>
+        <f>COUNTIF('Plano Mestre'!B2:B145,"Frontend")</f>
         <v>0</v>
       </c>
       <c r="C19" s="2">
-        <f>COUNTIFS('Plano Mestre'!B2:B143,"Frontend",'Plano Mestre'!I2:I143,"Concluído")</f>
+        <f>COUNTIFS('Plano Mestre'!B2:B145,"Frontend",'Plano Mestre'!I2:I145,"Concluído")</f>
         <v>0</v>
       </c>
     </row>
@@ -392,11 +392,11 @@
         </is>
       </c>
       <c r="B20" s="2">
-        <f>COUNTIF('Plano Mestre'!B2:B143,"Conteúdo")</f>
+        <f>COUNTIF('Plano Mestre'!B2:B145,"Conteúdo")</f>
         <v>0</v>
       </c>
       <c r="C20" s="2">
-        <f>COUNTIFS('Plano Mestre'!B2:B143,"Conteúdo",'Plano Mestre'!I2:I143,"Concluído")</f>
+        <f>COUNTIFS('Plano Mestre'!B2:B145,"Conteúdo",'Plano Mestre'!I2:I145,"Concluído")</f>
         <v>0</v>
       </c>
     </row>
@@ -407,11 +407,11 @@
         </is>
       </c>
       <c r="B21" s="2">
-        <f>COUNTIF('Plano Mestre'!B2:B143,"Qualidade")</f>
+        <f>COUNTIF('Plano Mestre'!B2:B145,"Qualidade")</f>
         <v>0</v>
       </c>
       <c r="C21" s="2">
-        <f>COUNTIFS('Plano Mestre'!B2:B143,"Qualidade",'Plano Mestre'!I2:I143,"Concluído")</f>
+        <f>COUNTIFS('Plano Mestre'!B2:B145,"Qualidade",'Plano Mestre'!I2:I145,"Concluído")</f>
         <v>0</v>
       </c>
     </row>
@@ -422,11 +422,11 @@
         </is>
       </c>
       <c r="B22" s="2">
-        <f>COUNTIF('Plano Mestre'!B2:B143,"Jurídico")</f>
+        <f>COUNTIF('Plano Mestre'!B2:B145,"Jurídico")</f>
         <v>0</v>
       </c>
       <c r="C22" s="2">
-        <f>COUNTIFS('Plano Mestre'!B2:B143,"Jurídico",'Plano Mestre'!I2:I143,"Concluído")</f>
+        <f>COUNTIFS('Plano Mestre'!B2:B145,"Jurídico",'Plano Mestre'!I2:I145,"Concluído")</f>
         <v>0</v>
       </c>
     </row>
@@ -437,11 +437,11 @@
         </is>
       </c>
       <c r="B23" s="2">
-        <f>COUNTIF('Plano Mestre'!B2:B143,"Lançamento")</f>
+        <f>COUNTIF('Plano Mestre'!B2:B145,"Lançamento")</f>
         <v>0</v>
       </c>
       <c r="C23" s="2">
-        <f>COUNTIFS('Plano Mestre'!B2:B143,"Lançamento",'Plano Mestre'!I2:I143,"Concluído")</f>
+        <f>COUNTIFS('Plano Mestre'!B2:B145,"Lançamento",'Plano Mestre'!I2:I145,"Concluído")</f>
         <v>0</v>
       </c>
     </row>
@@ -452,11 +452,11 @@
         </is>
       </c>
       <c r="B24" s="2">
-        <f>COUNTIF('Plano Mestre'!B2:B143,"Pós-lançamento")</f>
+        <f>COUNTIF('Plano Mestre'!B2:B145,"Pós-lançamento")</f>
         <v>0</v>
       </c>
       <c r="C24" s="2">
-        <f>COUNTIFS('Plano Mestre'!B2:B143,"Pós-lançamento",'Plano Mestre'!I2:I143,"Concluído")</f>
+        <f>COUNTIFS('Plano Mestre'!B2:B145,"Pós-lançamento",'Plano Mestre'!I2:I145,"Concluído")</f>
         <v>0</v>
       </c>
     </row>
@@ -467,11 +467,11 @@
         </is>
       </c>
       <c r="B25" s="2">
-        <f>COUNTIF('Plano Mestre'!B2:B143,"MPV de teste")</f>
+        <f>COUNTIF('Plano Mestre'!B2:B145,"MPV de teste")</f>
         <v>0</v>
       </c>
       <c r="C25" s="2">
-        <f>COUNTIFS('Plano Mestre'!B2:B143,"MPV de teste",'Plano Mestre'!I2:I143,"Concluído")</f>
+        <f>COUNTIFS('Plano Mestre'!B2:B145,"MPV de teste",'Plano Mestre'!I2:I145,"Concluído")</f>
         <v>0</v>
       </c>
     </row>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="N25" s="0" t="inlineStr">
         <is>
-          <t>Desenho em docs/HOME-E-ROTINA-DIARIA.md e protótipo navegável em docs/prototipo-home-rotina.html - 13 estados da home e rotina com perguntas desafios e modo misto - pendentes revisão visual e validação com casais na tarefa 30</t>
+          <t>Desenho em docs/HOME-E-ROTINA-DIARIA.md e protótipo navegável em docs/prototipo-home-rotina.html - 13 estados da home e rotina com perguntas desafios e modo misto - home do casal conectado aprovada visualmente pela Product Owner em 23/09/2026 com as quatro dinâmicas de Explorem juntos acima do cartão Gesto de hoje - pendente validação com casais na tarefa 30</t>
         </is>
       </c>
     </row>
@@ -2217,7 +2217,7 @@
       </c>
       <c r="N26" s="0" t="inlineStr">
         <is>
-          <t>Desenho em docs/PERGUNTAS-E-REVELACAO-MUTUA.md e protótipo docs/prototipo-perguntas-revelacao.html - discursiva múltipla escolha desafios espera correção pulo retomada e revelação bilateral - verificação de estados automatizada - validação visual e com casais pendentes na tarefa 30</t>
+          <t>Desenho em docs/PERGUNTAS-E-REVELACAO-MUTUA.md e protótipo docs/prototipo-perguntas-revelacao.html - discursiva múltipla escolha desafios espera correção pulo retomada e revelação bilateral - durante a revisão de 23/09/2026 a configuração recebeu seleção de temas por cápsulas quarto formato Múltipla escolha funcional e níveis Leve e Profunda com conteúdo ilustrativo do protótipo - verificação de estados automatizada - validação visual da configuração rodada e com casais pendentes na tarefa 30</t>
         </is>
       </c>
     </row>
@@ -2283,7 +2283,7 @@
       </c>
       <c r="N27" s="0" t="inlineStr">
         <is>
-          <t>Desenho em docs/TESTES-E-RESULTADOS.md e protótipo docs/prototipo-testes-resultados.html - formas de afeto e temperamentos experimentais com pausa revisão resultado parcial empate compartilhamento opcional e revogação - verificação de estados em scripts/validate-tests-prototype.mjs - revisão visual editorial especializada e validação com casais pendentes</t>
+          <t>Desenho em docs/TESTES-E-RESULTADOS.md e protótipo docs/prototipo-testes-resultados.html - formas de afeto e temperamentos experimentais com pausa revisão resultado parcial empate compartilhamento opcional e revogação - as 32 combinações da implementação binária atual foram mapeadas em Conteúdo/mapeamento-linguagens-do-amor.xlsx com gerador e validador próprios - o mapeamento evidenciou desempate atual por primeira ocorrência divergente da regra TR-11 e pendente de decisão editorial - revisão visual especializada e validação com casais pendentes</t>
         </is>
       </c>
     </row>
@@ -2332,11 +2332,11 @@
         </is>
       </c>
       <c r="J28" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K28" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L28" s="0" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="N28" s="0" t="inlineStr">
         <is>
-          <t>Home rotina diária perguntas com revelação e testes com resultados desenhados em protótipos HTML responsivos na pasta docs - demais telas e validação visual completa pendentes</t>
+          <t>Revisão página por página iniciada em 21/09/2026 - onboarding cadastro pareamento convite Home Correio do Amor e Perfil aprovados visualmente pela Product Owner até 23/09/2026 - configuração de Perguntas que aproximam recebeu Múltipla escolha temas com corações e níveis Leve e Profunda em /wireframes/perguntas - página inicial de As linguagens do amor disponibilizada em /wireframes/linguagens-do-amor para a próxima revisão - evidências desktop e mobile em docs - primeira rodada permanece disponível em /wireframes/pergunta</t>
         </is>
       </c>
     </row>
@@ -4217,12 +4217,12 @@
       </c>
       <c r="D57" s="0" t="inlineStr">
         <is>
-          <t>Implementar linguagens do amor e resultado</t>
+          <t>Implementar formas de afeto e resultado bilateral</t>
         </is>
       </c>
       <c r="E57" s="0" t="inlineStr">
         <is>
-          <t>Serviço de avaliação</t>
+          <t>Serviço de avaliação e composição consentida</t>
         </is>
       </c>
       <c r="F57" s="0" t="inlineStr">
@@ -4232,7 +4232,7 @@
       </c>
       <c r="G57" s="0" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>49,77</t>
         </is>
       </c>
       <c r="H57" s="0" t="inlineStr">
@@ -4246,7 +4246,7 @@
         </is>
       </c>
       <c r="J57" s="0">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="K57" s="0" t="inlineStr">
         <is>
@@ -4263,7 +4263,7 @@
       </c>
       <c r="N57" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>Manter resultado individual privado e versionado - compor visão bilateral somente quando as duas pessoas concluírem a mesma versão e compartilharem - apresentar forças complementaridades oportunidades e sugestões aprovadas sem nota de compatibilidade - revogação ou desvinculação encerra acesso</t>
         </is>
       </c>
     </row>
@@ -4364,7 +4364,7 @@
       </c>
       <c r="G59" s="0" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>49,56</t>
         </is>
       </c>
       <c r="H59" s="0" t="inlineStr">
@@ -4395,7 +4395,7 @@
       </c>
       <c r="N59" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>Incluir sugestão semanal derivada do resultado bilateral somente por opt-in individual - frequência dia horário pausa e desligamento configuráveis - cancelar ao revogar compartilhamento ou vínculo - payload de push neutro sem resultado ou tema íntimo</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="K63" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="L63" s="0" t="inlineStr">
@@ -4659,7 +4659,7 @@
       </c>
       <c r="N63" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>Layout de cadastro aprovado pela Product Owner em 22/09/2026 na rota /wireframes/cadastro com chamada removida título em duas linhas e estrela dourada - integração funcional existente preservada - modo de login permanece pendente de revisão</t>
         </is>
       </c>
     </row>
@@ -4712,7 +4712,7 @@
       </c>
       <c r="K64" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="L64" s="0" t="inlineStr">
@@ -4725,7 +4725,7 @@
       </c>
       <c r="N64" s="0" t="inlineStr">
         <is>
-          <t>Criação entrada e espera implementadas - reaberto na revisão: erro de atualização sem mensagem e cópia pode informar sucesso sem clipboard - integração e validação completas pendentes</t>
+          <t>Criação entrada e espera implementadas - telas de escolha e de convite e espera aprovadas visualmente pela Product Owner em 23/09/2026 nas rotas /wireframes/conectar e /wireframes/convite - indicadores das três etapas ampliados e iluminados em dourado - erro de atualização sem mensagem e confirmação de cópia sem clipboard permanecem pendentes antes da validação funcional completa</t>
         </is>
       </c>
     </row>
@@ -4791,7 +4791,7 @@
       </c>
       <c r="N65" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>Tela atual de conta vínculo código do casal atualização e saída aprovada visualmente pela Product Owner em 23/09/2026 na rota /wireframes/perfil - preferências privacidade e gestão de vínculo previstas no escopo completo permanecem pendentes</t>
         </is>
       </c>
     </row>
@@ -4857,7 +4857,7 @@
       </c>
       <c r="N66" s="0" t="inlineStr">
         <is>
-          <t>Home atual parcial - integrar estados em docs/HOME-E-ROTINA-DIARIA.md com pendências reais e progresso confirmado sem valores demonstrativos</t>
+          <t>Home atual parcial aprovada visualmente pela Product Owner em 23/09/2026 na rota /wireframes/home com Explorem juntos e as quatro dinâmicas primeiro e Gesto de hoje abaixo sem duplicação - ainda integrar estados em docs/HOME-E-ROTINA-DIARIA.md com pendências reais e progresso confirmado sem valores demonstrativos</t>
         </is>
       </c>
     </row>
@@ -4906,7 +4906,7 @@
         </is>
       </c>
       <c r="J67" s="0">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K67" s="0" t="inlineStr">
         <is>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="N67" s="0" t="inlineStr">
         <is>
-          <t>Jogo local por temas implementado em 109 - níveis leve médio profundo e catálogo remoto ainda pendentes - harmonizar formato e mecânica na tarefa 112</t>
+          <t>Configuração do jogo local em /wireframes/perguntas ajustada em 23/09/2026 com temas em cápsulas selecionáveis escolha funcional entre Leve e Profunda quatro formatos em grade e Múltipla escolha com seleção e confirmação separadas - o nível altera perguntas desafios e alternativas da sessão - conteúdo atual é ilustrativo e aguarda aprovação editorial da tarefa 108 - catálogo remoto e harmonização na tarefa 112 permanecem pendentes</t>
         </is>
       </c>
     </row>
@@ -5075,7 +5075,7 @@
       </c>
       <c r="D70" s="0" t="inlineStr">
         <is>
-          <t>Implementar teste de linguagens do amor</t>
+          <t>Implementar formas de afeto e visão bilateral</t>
         </is>
       </c>
       <c r="E70" s="0" t="inlineStr">
@@ -5104,7 +5104,7 @@
         </is>
       </c>
       <c r="J70" s="0">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="K70" s="0" t="inlineStr">
         <is>
@@ -5121,7 +5121,7 @@
       </c>
       <c r="N70" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>Primeira pergunta da experiência individual disponibilizada para revisão visual em /wireframes/linguagens-do-amor em 23/09/2026 - lógica binária atual documentada em planilha com 32 combinações pontuações empates e resultados - desempate por primeira ocorrência deve ser substituído ou aprovado editorialmente antes da validação - preservar resultado individual e compartilhamento explícito - após duas conclusões compatíveis apresentar forças compartilhadas formas complementares oportunidades de cuidado e sugestões do que cada pessoa pode experimentar pela outra - sem diagnóstico déficit ou nota de compatibilidade</t>
         </is>
       </c>
     </row>
@@ -5288,7 +5288,7 @@
       </c>
       <c r="G73" s="0" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>58,69</t>
         </is>
       </c>
       <c r="H73" s="0" t="inlineStr">
@@ -5302,7 +5302,7 @@
         </is>
       </c>
       <c r="J73" s="0">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="K73" s="0" t="inlineStr">
         <is>
@@ -5319,7 +5319,7 @@
       </c>
       <c r="N73" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>Oferecer ativação individual de sugestão semanal após visão bilateral - permitir configurar pausar e desligar - push neutro abre conteúdo apenas após autenticação e não registra gesto como prova ou progresso</t>
         </is>
       </c>
     </row>
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="J78" s="0">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="K78" s="0" t="inlineStr">
         <is>
@@ -5649,7 +5649,7 @@
       </c>
       <c r="N78" s="0" t="inlineStr">
         <is>
-          <t>Validar lotes e recomendações antes de publicação - distinguir conteúdo candidato de aprovado e seleção mínima de 60 atividades - conteúdo íntimo restrito conforme baseline do piloto</t>
+          <t>Produzir matriz candidata e validar sugestões de cuidado por combinação de formas de afeto além dos lotes de atividades - recomendações devem ser pequenas adaptáveis e orientadas pela preferência de quem recebe - distinguir conteúdo candidato de aprovado - seleção mínima de 60 atividades e conteúdo íntimo restrito conforme baseline</t>
         </is>
       </c>
     </row>
@@ -6872,7 +6872,7 @@
       </c>
       <c r="G97" s="0" t="inlineStr">
         <is>
-          <t>87,90,92-95,77,116,117,119,121,122</t>
+          <t>87,90,92-95,77,116,117,119,121,122,143</t>
         </is>
       </c>
       <c r="H97" s="0" t="inlineStr">
@@ -6903,7 +6903,7 @@
       </c>
       <c r="N97" s="0" t="inlineStr">
         <is>
-          <t>UAT do ciclo bilateral conforme baseline 112 - mecânicas 113 e 114 entram no aceite se mantidas para o piloto - reunir evidências de conteúdo privacidade fornecedores e operação</t>
+          <t>UAT do ciclo bilateral conforme baseline 112 - mecânicas 113 e 114 entram no aceite do primeiro piloto - resultado bilateral e lembrete semanal da tarefa 143 são obrigatórios para o aceite pré-lançamento - reunir evidências de conteúdo privacidade fornecedores e operação</t>
         </is>
       </c>
     </row>
@@ -7695,7 +7695,7 @@
       </c>
       <c r="N109" s="0" t="inlineStr">
         <is>
-          <t>75 perguntas de múltipla escolha candidatas em Conteúdo/banco-de-perguntas-conectadois.xlsx - produção precede revisão 76 e parecer 77 - pendentes revisão editorial aprovação e seleção do lote do piloto</t>
+          <t>75 perguntas de múltipla escolha candidatas em Conteúdo/banco-de-perguntas-conectadois.xlsx - interface funcional usa temporariamente pergunta e quatro alternativas ilustrativas já definidas no protótipo sem promover conteúdo candidato - produção precede revisão 76 e parecer 77 - pendentes revisão editorial aprovação e seleção do lote do piloto</t>
         </is>
       </c>
     </row>
@@ -7761,7 +7761,7 @@
       </c>
       <c r="N110" s="0" t="inlineStr">
         <is>
-          <t>Onze temas com dois formatos e modo misto - respostas por jogador e confirmação individual de desafios - pular e reiniciar disponíveis</t>
+          <t>Onze temas apresentados em cápsulas responsivas com ícones de coração seleção de nível Leve ou Profunda e quatro formatos Perguntas discursivas Múltipla escolha Desafios e modo misto - múltipla escolha exige seleção seguida de confirmação - respostas por jogador confirmação individual de desafios pular e reiniciar disponíveis - configuração ajustada em /wireframes/perguntas em 23/09/2026</t>
         </is>
       </c>
     </row>
@@ -7872,7 +7872,7 @@
       </c>
       <c r="I112" s="0" t="inlineStr">
         <is>
-          <t>Não iniciado</t>
+          <t>Em andamento</t>
         </is>
       </c>
       <c r="J112" s="0">
@@ -7880,7 +7880,7 @@
       </c>
       <c r="K112" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L112" s="0" t="inlineStr">
@@ -7889,11 +7889,11 @@
         </is>
       </c>
       <c r="M112" s="3">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="N112" s="0" t="inlineStr">
         <is>
-          <t>Implementar modelo de partidas e snapshots de conteúdo - integrar respostas e progresso com transações e testes de concorrência</t>
+          <t>Primeira fatia em /api/v1/game-sessions cria e retoma partidas autenticadas com idempotência isolamento por casal participantes e snapshots do catálogo atual - validação ponta a ponta em scripts/validate-game-sessions.mjs e contrato marcado como parcial - pendentes persistência PostgreSQL respostas progresso transacional retomada no frontend e testes de concorrência</t>
         </is>
       </c>
     </row>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="I113" s="0" t="inlineStr">
         <is>
-          <t>Não iniciado</t>
+          <t>Concluído</t>
         </is>
       </c>
       <c r="J113" s="0">
@@ -7946,20 +7946,20 @@
       </c>
       <c r="K113" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L113" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="M113" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N113" s="0" t="inlineStr">
         <is>
-          <t>Conciliar perguntas desafios e misto com resposta guardada adivinhação e coincidências - decidir primeiro piloto e atualizar PRD escopo MoSCoW modelo e cronograma - estimativa preliminar</t>
+          <t>Baseline aprovada em docs/DECISAO-ESCOPO-PILOTO-2026-09-21.md - primeiro piloto inclui três níveis perguntas desafios modo misto e desafio na adivinhação - resultado bilateral e lembrete semanal ficam na iteração seguinte pela tarefa 143 e são obrigatórios antes da UAT e do lançamento - PRD escopo MoSCoW e rastreabilidade atualizados</t>
         </is>
       </c>
     </row>
@@ -8008,7 +8008,7 @@
         </is>
       </c>
       <c r="J114" s="0">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="K114" s="0" t="inlineStr">
         <is>
@@ -8025,7 +8025,7 @@
       </c>
       <c r="N114" s="0" t="inlineStr">
         <is>
-          <t>Já previsto no escopo MVP - execução condicionada à decisão 112 - incluir modelo de tentativas API interface e testes de autoria - estimativa preliminar</t>
+          <t>Incluir perguntas de preferência e variação de gesto ou desafio desejado - palpite e revelação separados do aceite bilateral para executar adaptar trocar ou pular sem prova - incluir modelo de tentativas API interface autoria consentimento e testes - execução condicionada à baseline 112</t>
         </is>
       </c>
     </row>
@@ -9512,7 +9512,7 @@
       </c>
       <c r="G137" s="0" t="inlineStr">
         <is>
-          <t>135,142</t>
+          <t>135</t>
         </is>
       </c>
       <c r="H137" s="0" t="inlineStr">
@@ -9522,7 +9522,7 @@
       </c>
       <c r="I137" s="0" t="inlineStr">
         <is>
-          <t>Não iniciado</t>
+          <t>Concluído</t>
         </is>
       </c>
       <c r="J137" s="0">
@@ -9539,11 +9539,11 @@
         </is>
       </c>
       <c r="M137" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N137" s="0" t="inlineStr">
         <is>
-          <t>Cada casal usa as experiências sem mediação e envia os três sinais do produto com sugestão de melhoria opcional — não há entrevistas nem etapa de pesquisa dentro do MPV — iniciar após a nova passagem física da versão ampliada</t>
+          <t>Validação com cinco casais aceita como concluída pela Product Owner em 21/09/2026 - decisão e limites registrados em docs/VALIDACAO-MPV-CINCO-CASAIS-2026-09-21.md - continuar o formato com ajustes - os comentários qualitativos foram aceitos como achados da rodada e os 5 sinais anônimos da API permanecem apenas como evidência agregada - a passagem física 142 segue como hardening de qualidade sem bloquear este aceite</t>
         </is>
       </c>
     </row>
@@ -9588,7 +9588,7 @@
       </c>
       <c r="I138" s="0" t="inlineStr">
         <is>
-          <t>Não iniciado</t>
+          <t>Concluído</t>
         </is>
       </c>
       <c r="J138" s="0">
@@ -9605,11 +9605,11 @@
         </is>
       </c>
       <c r="M138" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N138" s="0" t="inlineStr">
         <is>
-          <t>Registrar continuar ajustar ou encerrar o formato e quais evidências devem orientar a futura revisão do plano completo sem alterá-lo automaticamente</t>
+          <t>Concluído em 21/09/2026 com registro em docs/FEEDBACK-DE-PRODUTO-2026-09-21.md e docs/VALIDACAO-MPV-CINCO-CASAIS-2026-09-21.md - PRD escopo fluxos e tarefas 56 58 66 69 72 77 112 e 113 atualizados - decisão de continuar o formato com ajustes sem interpretar os achados como prevalência estatística</t>
         </is>
       </c>
     </row>
@@ -9943,8 +9943,140 @@
         </is>
       </c>
     </row>
+    <row r="144">
+      <c r="A144" s="0">
+        <v>143</v>
+      </c>
+      <c r="B144" s="0" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="C144" s="0" t="inlineStr">
+        <is>
+          <t>Integração</t>
+        </is>
+      </c>
+      <c r="D144" s="0" t="inlineStr">
+        <is>
+          <t>Integrar resultado bilateral e lembrete semanal na iteração pré-lançamento</t>
+        </is>
+      </c>
+      <c r="E144" s="0" t="inlineStr">
+        <is>
+          <t>Jornada bilateral e lembrete validados</t>
+        </is>
+      </c>
+      <c r="F144" s="0" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+      <c r="G144" s="0" t="inlineStr">
+        <is>
+          <t>56,58,69,72,77,90,119</t>
+        </is>
+      </c>
+      <c r="H144" s="0" t="inlineStr">
+        <is>
+          <t>Liderança Técnica</t>
+        </is>
+      </c>
+      <c r="I144" s="0" t="inlineStr">
+        <is>
+          <t>Não iniciado</t>
+        </is>
+      </c>
+      <c r="J144" s="0">
+        <v>24</v>
+      </c>
+      <c r="K144" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L144" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M144" s="3">
+        <v>0</v>
+      </c>
+      <c r="N144" s="0" t="inlineStr">
+        <is>
+          <t>Executar depois do primeiro piloto e antes da UAT - integrar duas conclusões compatíveis compartilhamento revogável forças complementaridades oportunidades sugestões aprovadas e lembrete semanal opt-in - testar autorização desvinculação privacidade push neutro acessibilidade e cancelamento - gate obrigatório das tarefas 96 a 98 e do lançamento</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="0">
+        <v>144</v>
+      </c>
+      <c r="B145" s="0" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="C145" s="0" t="inlineStr">
+        <is>
+          <t>Casal</t>
+        </is>
+      </c>
+      <c r="D145" s="0" t="inlineStr">
+        <is>
+          <t>Implementar Correio do Amor entre contas pareadas</t>
+        </is>
+      </c>
+      <c r="E145" s="0" t="inlineStr">
+        <is>
+          <t>Envio e histórico de recados do casal</t>
+        </is>
+      </c>
+      <c r="F145" s="0" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="G145" s="0" t="inlineStr">
+        <is>
+          <t>27,49,63</t>
+        </is>
+      </c>
+      <c r="H145" s="0" t="inlineStr">
+        <is>
+          <t>Engenharia Frontend e Backend</t>
+        </is>
+      </c>
+      <c r="I145" s="0" t="inlineStr">
+        <is>
+          <t>Em andamento</t>
+        </is>
+      </c>
+      <c r="J145" s="0">
+        <v>16</v>
+      </c>
+      <c r="K145" s="0" t="inlineStr">
+        <is>
+          <t>23/09/2026</t>
+        </is>
+      </c>
+      <c r="L145" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M145" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="N145" s="0" t="inlineStr">
+        <is>
+          <t>Primeira fatia implementada na aba Nós e em /wireframes/correio com composição de até 280 caracteres histórico responsivo persistência no armazenamento da API autorização restrita ao casal e teste automatizado de envio e leitura pela conta parceira - visual aprovado pela Product Owner em 23/09/2026 - contrato parcial em docs/openapi-v1.json - persistência PostgreSQL definitiva permanece pendente</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N143"/>
+  <autoFilter ref="A1:N145"/>
   <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
 </worksheet>
 </file>
@@ -10119,12 +10251,12 @@
       </c>
       <c r="D5" s="0" t="inlineStr">
         <is>
-          <t>Não iniciado</t>
+          <t>Concluído</t>
         </is>
       </c>
       <c r="E5" s="0" t="inlineStr">
         <is>
-          <t>Sinais de cinco casais registrados como insumo para revisão futura do plano completo</t>
+          <t>Feedback de cinco casais registrado e incorporado ao PRD escopo fluxos e backlog</t>
         </is>
       </c>
       <c r="F5" s="0" t="inlineStr">
@@ -10134,7 +10266,7 @@
       </c>
       <c r="G5" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>21/09/2026</t>
         </is>
       </c>
     </row>
@@ -10290,7 +10422,7 @@
         </is>
       </c>
       <c r="C10" s="0">
-        <v>75</v>
+        <v>143</v>
       </c>
       <c r="D10" s="0" t="inlineStr">
         <is>
@@ -10299,7 +10431,7 @@
       </c>
       <c r="E10" s="0" t="inlineStr">
         <is>
-          <t>Jornada bilateral validada incluindo 111 e 116 e métricas 106-107 — 113-114 conforme decisão 112</t>
+          <t>Núcleo do primeiro piloto validado e integração pré-lançamento 143 concluída com resultado bilateral e lembrete semanal</t>
         </is>
       </c>
       <c r="F10" s="0" t="inlineStr">
@@ -10369,7 +10501,7 @@
       </c>
       <c r="E12" s="0" t="inlineStr">
         <is>
-          <t>QA segurança acessibilidade privacidade UAT e restauração 118 sem bloqueador — PWA 119 validada</t>
+          <t>QA segurança acessibilidade privacidade UAT integração 143 e restauração 118 sem bloqueador — PWA 119 validada</t>
         </is>
       </c>
       <c r="F12" s="0" t="inlineStr">
